--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.1797855516353</v>
+        <v>565.0273964200943</v>
       </c>
       <c r="E2" t="n">
-        <v>15398.187527036</v>
+        <v>15391.25475424421</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6212847081660688</v>
+        <v>0.6128775387044489</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014052653433979</v>
+        <v>0.5014408809024313</v>
       </c>
       <c r="H2" t="n">
-        <v>1.239086924507203</v>
+        <v>1.222232893340223</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.5879758410973</v>
+        <v>221.8896992794857</v>
       </c>
       <c r="E3" t="n">
-        <v>6327.610747175488</v>
+        <v>6309.927060681516</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2503215934471397</v>
+        <v>0.2451927029172301</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010516979147806</v>
+        <v>0.6010624725402997</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4164726500491996</v>
+        <v>0.4079321436937498</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,45 +598,45 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907366667406511</v>
+        <v>0.8907314848716131</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06775660916276</v>
+        <v>1.067693698413468</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.9798134149969</v>
+        <v>36.66947204912138</v>
       </c>
       <c r="E4" t="n">
-        <v>2270.489823996775</v>
+        <v>456.0018080898822</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7586708739727697</v>
+        <v>-0.3464963061129638</v>
       </c>
       <c r="G4" t="n">
-        <v>1.114686376552082</v>
+        <v>0.5644370068319943</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6806137492408136</v>
+        <v>-0.6138794974796878</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3422195892575038</v>
+        <v>0.3496897913141569</v>
       </c>
       <c r="J4" t="n">
         <v>267</v>
@@ -652,45 +652,45 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735767432014794</v>
+        <v>0.7366372264595562</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052820104585572</v>
+        <v>0.8291811199668735</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.81546869681902</v>
+        <v>36.65981428152553</v>
       </c>
       <c r="E5" t="n">
-        <v>452.6283481928581</v>
+        <v>2298.964214513857</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3434991031119429</v>
+        <v>0.736428912928762</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5644460804764754</v>
+        <v>1.114782468140612</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6085596392519533</v>
+        <v>0.6606032423142424</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3496897913141569</v>
+        <v>0.3422195892575038</v>
       </c>
       <c r="J5" t="n">
         <v>267</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366425613437927</v>
+        <v>0.4736587740780721</v>
       </c>
       <c r="N5" t="n">
-        <v>0.829259354063403</v>
+        <v>1.053018446108608</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.69644789380958</v>
+        <v>10.65595738049454</v>
       </c>
       <c r="E6" t="n">
-        <v>244.9836527064039</v>
+        <v>243.5395680897134</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3197655883065118</v>
+        <v>-0.3246247703162967</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7182286700965943</v>
+        <v>0.7182315574351763</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4452141798565444</v>
+        <v>-0.4519778711416416</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7511315722235422</v>
+        <v>0.751147828279358</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075944485377914</v>
+        <v>1.07589567407869</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.39202323505474</v>
+        <v>10.54434666189083</v>
       </c>
       <c r="E7" t="n">
-        <v>1457.711721151102</v>
+        <v>1495.893310916934</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5189087819127034</v>
+        <v>-0.509588087084621</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8079173588425211</v>
+        <v>0.8081360232925089</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6422795304907526</v>
+        <v>-0.6305721715119894</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6772701600094486</v>
+        <v>0.6767575702983346</v>
       </c>
       <c r="N7" t="n">
-        <v>1.091289535068881</v>
+        <v>1.090681259592819</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.464974532960788</v>
+        <v>9.38840474718603</v>
       </c>
       <c r="E8" t="n">
-        <v>490.5468447135377</v>
+        <v>493.2605306406035</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3630193204061807</v>
+        <v>-0.3689633445285231</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174295667228352</v>
+        <v>1.174314966490552</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3091379203186556</v>
+        <v>-0.314194534734725</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395339781696092</v>
+        <v>0.7395453347305331</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731995266818657</v>
+        <v>1.731927307979725</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.307983385412979</v>
+        <v>7.268494232969219</v>
       </c>
       <c r="E9" t="n">
-        <v>225.6552441398756</v>
+        <v>225.8691914814227</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4156117556386283</v>
+        <v>0.4021045595396797</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824277930963312</v>
+        <v>0.482501949157374</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8615004392079851</v>
+        <v>0.8333739588863885</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788689731992013</v>
+        <v>0.6789326913218838</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531747533958669</v>
+        <v>0.6532900674550532</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.781417670057059</v>
+        <v>6.745430456448645</v>
       </c>
       <c r="E10" t="n">
-        <v>274.1468706099368</v>
+        <v>273.3315124125779</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.254917251931126</v>
+        <v>-0.2627433879617302</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9628729687781589</v>
+        <v>0.9629220391072247</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2647465036375506</v>
+        <v>-0.2728604988679388</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7139773524108879</v>
+        <v>0.7140134968092496</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371085508017977</v>
+        <v>1.371127402018547</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.561215370685046</v>
+        <v>6.527576419226462</v>
       </c>
       <c r="E11" t="n">
-        <v>558.9665649092937</v>
+        <v>552.3230671573039</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9410541528813237</v>
+        <v>0.9250369257469993</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258939986973493</v>
+        <v>0.8259266243519866</v>
       </c>
       <c r="H11" t="n">
-        <v>1.139436966929911</v>
+        <v>1.119998918151808</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643153042447114</v>
+        <v>0.6643514626507132</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094232671535177</v>
+        <v>1.094257731724856</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.309119903268258</v>
+        <v>6.294682158461277</v>
       </c>
       <c r="E12" t="n">
-        <v>142.9198722196133</v>
+        <v>141.1874189320298</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2775218642460677</v>
+        <v>-0.2792245088602159</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6618971952769398</v>
+        <v>0.6618924531841418</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4192824296980919</v>
+        <v>-0.421857822244325</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890978649975358</v>
+        <v>0.7890511820102916</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041675665857201</v>
+        <v>1.041532596242905</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.640966472501429</v>
+        <v>4.59997447101991</v>
       </c>
       <c r="E13" t="n">
-        <v>266.9777683110001</v>
+        <v>259.845731735295</v>
       </c>
       <c r="F13" t="n">
-        <v>1.709048256584516</v>
+        <v>1.667192992979428</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8652908657676719</v>
+        <v>0.8654562099808097</v>
       </c>
       <c r="H13" t="n">
-        <v>1.975114177437059</v>
+        <v>1.926374753283468</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6040531960029941</v>
+        <v>0.6041281801314307</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042433634160564</v>
+        <v>1.042688191234423</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.538546114560249</v>
+        <v>4.538033092495079</v>
       </c>
       <c r="E14" t="n">
-        <v>135.5147331937339</v>
+        <v>134.7773232408184</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4097789842287906</v>
+        <v>-0.409163446948416</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8547353261261988</v>
+        <v>0.8547363199048116</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4794220757038045</v>
+        <v>-0.4787013695568509</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7604134226377498</v>
+        <v>0.7603402936331376</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296261247563651</v>
+        <v>1.296046032955549</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.080808887226178</v>
+        <v>4.074475419511248</v>
       </c>
       <c r="E15" t="n">
-        <v>311.5881750363473</v>
+        <v>303.5918450257223</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04959782850041261</v>
+        <v>-0.04770939544814712</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7948330145811707</v>
+        <v>0.7948277833348151</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06240031250658063</v>
+        <v>-0.06002482103478497</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7177040990260132</v>
+        <v>0.717668043402535</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137712250020791</v>
+        <v>1.137566803650502</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.965156020450405</v>
+        <v>3.915281501056894</v>
       </c>
       <c r="E16" t="n">
-        <v>197.1500988987758</v>
+        <v>199.4990177172872</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4356081064473512</v>
+        <v>0.4166931326974341</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9621148273089083</v>
+        <v>0.9622633377977453</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4527610365030675</v>
+        <v>0.4330344057907123</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.515886499272475</v>
+        <v>0.5159809085634119</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9899019505082464</v>
+        <v>0.9901656012182042</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.337013952637049</v>
+        <v>3.324512369535344</v>
       </c>
       <c r="E17" t="n">
-        <v>109.7537478340919</v>
+        <v>107.7769525415004</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2251968130947322</v>
+        <v>-0.2286794815264216</v>
       </c>
       <c r="G17" t="n">
-        <v>0.757341651293717</v>
+        <v>0.7573569430496023</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2973516809884195</v>
+        <v>-0.3019441276996974</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244610679523354</v>
+        <v>0.7244709221879923</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09425364954089</v>
+        <v>1.094212904957354</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.122382723366384</v>
+        <v>3.119691399625707</v>
       </c>
       <c r="E18" t="n">
-        <v>76.93458674673656</v>
+        <v>76.41722330837844</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4697990833404916</v>
+        <v>-0.4699601090997502</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498554691626944</v>
+        <v>0.7498552626498134</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.62651951297372</v>
+        <v>-0.626734427973501</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645579311014338</v>
+        <v>0.7644995772104208</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143402324934667</v>
+        <v>1.143233535792099</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.940149160569367</v>
+        <v>2.931446195626162</v>
       </c>
       <c r="E19" t="n">
-        <v>106.9751386130635</v>
+        <v>106.7525732763789</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09904094571546218</v>
+        <v>0.09716684696747246</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837732383141865</v>
+        <v>0.4837946706531797</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2047259704993025</v>
+        <v>0.200843152811679</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7179287339464095</v>
+        <v>0.7180007076357189</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926826112649476</v>
+        <v>0.6927335387059551</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.578669913367356</v>
+        <v>2.565536809819419</v>
       </c>
       <c r="E20" t="n">
-        <v>141.0610064876083</v>
+        <v>141.4008460330726</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.328070603447956</v>
+        <v>-0.3326262885978836</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825527249733916</v>
+        <v>0.7825575736175814</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4192313092502631</v>
+        <v>-0.4250502452621214</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328248652057087</v>
+        <v>0.7328352676965615</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14373369175178</v>
+        <v>1.143675776729498</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>565.0273964200943</v>
+        <v>565.9273607147156</v>
       </c>
       <c r="E2" t="n">
-        <v>15391.25475424421</v>
+        <v>15041.57739948019</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6128775387044489</v>
+        <v>0.6172580344639913</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014408809024313</v>
+        <v>0.50141748255897</v>
       </c>
       <c r="H2" t="n">
-        <v>1.222232893340223</v>
+        <v>1.231026152725733</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>221.8896992794857</v>
+        <v>222.352025853045</v>
       </c>
       <c r="E3" t="n">
-        <v>6309.927060681516</v>
+        <v>6152.307455230985</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2451927029172301</v>
+        <v>0.2494079416178669</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010624725402997</v>
+        <v>0.6010521337214025</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4079321436937498</v>
+        <v>0.41495226058622</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907314848716131</v>
+        <v>0.8907232543373431</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067693698413468</v>
+        <v>1.067715289547704</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.66947204912138</v>
+        <v>36.75130642264449</v>
       </c>
       <c r="E4" t="n">
-        <v>456.0018080898822</v>
+        <v>453.057659487099</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3464963061129638</v>
+        <v>-0.3449981649042384</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5644370068319943</v>
+        <v>0.5644381953194144</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6138794974796878</v>
+        <v>-0.6112239883217057</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7366372264595562</v>
+        <v>0.7366377715099039</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8291811199668735</v>
+        <v>0.8292221727754897</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.65981428152553</v>
+        <v>36.65764044615386</v>
       </c>
       <c r="E5" t="n">
-        <v>2298.964214513857</v>
+        <v>2239.129445068542</v>
       </c>
       <c r="F5" t="n">
-        <v>0.736428912928762</v>
+        <v>0.7377954523407302</v>
       </c>
       <c r="G5" t="n">
-        <v>1.114782468140612</v>
+        <v>1.114773561643499</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6606032423142424</v>
+        <v>0.6618343650463022</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4736587740780721</v>
+        <v>0.4736169276290457</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053018446108608</v>
+        <v>1.052966136268671</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.65595738049454</v>
+        <v>10.65602045265007</v>
       </c>
       <c r="E6" t="n">
-        <v>243.5395680897134</v>
+        <v>239.8459954474154</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3246247703162967</v>
+        <v>-0.3240178842757802</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7182315574351763</v>
+        <v>0.7182283768227099</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4519778711416416</v>
+        <v>-0.4511348962695774</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.751147828279358</v>
+        <v>0.7511562613085908</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07589567407869</v>
+        <v>1.075953194823907</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.54434666189083</v>
+        <v>10.64375460053239</v>
       </c>
       <c r="E7" t="n">
-        <v>1495.893310916934</v>
+        <v>1520.684739337585</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.509588087084621</v>
+        <v>-0.50557884372077</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8081360232925089</v>
+        <v>0.8083319759587526</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6305721715119894</v>
+        <v>-0.6254594136537889</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6767575702983346</v>
+        <v>0.6766638461877814</v>
       </c>
       <c r="N7" t="n">
-        <v>1.090681259592819</v>
+        <v>1.090845538646514</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.38840474718603</v>
+        <v>9.439518614824522</v>
       </c>
       <c r="E8" t="n">
-        <v>493.2605306406035</v>
+        <v>480.6385457910034</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3689633445285231</v>
+        <v>-0.3633912599882285</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174314966490552</v>
+        <v>1.174295296711044</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.314194534734725</v>
+        <v>-0.3094547521445513</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395453347305331</v>
+        <v>0.7395155030514716</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731927307979725</v>
+        <v>1.731909251840086</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.268494232969219</v>
+        <v>7.285672071831782</v>
       </c>
       <c r="E9" t="n">
-        <v>225.8691914814227</v>
+        <v>222.4360916693339</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4021045595396797</v>
+        <v>0.4094462660043718</v>
       </c>
       <c r="G9" t="n">
-        <v>0.482501949157374</v>
+        <v>0.4824446556581781</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8333739588863885</v>
+        <v>0.8486906450352989</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6789326913218838</v>
+        <v>0.6788923182142826</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532900674550532</v>
+        <v>0.6532041304550096</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.745430456448645</v>
+        <v>6.762663511756775</v>
       </c>
       <c r="E10" t="n">
-        <v>273.3315124125779</v>
+        <v>268.4153121637377</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2627433879617302</v>
+        <v>-0.2564562788909202</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9629220391072247</v>
+        <v>0.9628760684818052</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2728604988679388</v>
+        <v>-0.2663440158973753</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7140134968092496</v>
+        <v>0.7139756418246304</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371127402018547</v>
+        <v>1.371053229902135</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.527576419226462</v>
+        <v>6.560510720949376</v>
       </c>
       <c r="E11" t="n">
-        <v>552.3230671573039</v>
+        <v>543.5792575364828</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9250369257469993</v>
+        <v>0.9443212861846522</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8259266243519866</v>
+        <v>0.8258946976991463</v>
       </c>
       <c r="H11" t="n">
-        <v>1.119998918151808</v>
+        <v>1.143391874067517</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643514626507132</v>
+        <v>0.6642864592158219</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094257731724856</v>
+        <v>1.094159425035932</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.294682158461277</v>
+        <v>6.314355084637901</v>
       </c>
       <c r="E12" t="n">
-        <v>141.1874189320298</v>
+        <v>138.298416441444</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2792245088602159</v>
+        <v>-0.2752499946916865</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6618924531841418</v>
+        <v>0.6619129772334166</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.421857822244325</v>
+        <v>-0.4158401544597947</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890511820102916</v>
+        <v>0.7890115980400277</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041532596242905</v>
+        <v>1.041561242071271</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.59997447101991</v>
+        <v>4.611738024079757</v>
       </c>
       <c r="E13" t="n">
-        <v>259.845731735295</v>
+        <v>252.6724118283832</v>
       </c>
       <c r="F13" t="n">
-        <v>1.667192992979428</v>
+        <v>1.687323683736155</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8654562099808097</v>
+        <v>0.8653516565803235</v>
       </c>
       <c r="H13" t="n">
-        <v>1.926374753283468</v>
+        <v>1.949870519002739</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6041281801314307</v>
+        <v>0.6040791817622474</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042688191234423</v>
+        <v>1.042526315548181</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.538033092495079</v>
+        <v>4.536024385818279</v>
       </c>
       <c r="E14" t="n">
-        <v>134.7773232408184</v>
+        <v>132.6362651365112</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.409163446948416</v>
+        <v>-0.4079318557957841</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8547363199048116</v>
+        <v>0.8547410608835163</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4787013695568509</v>
+        <v>-0.4772578204843921</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7603402936331376</v>
+        <v>0.7603627135529519</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296046032955549</v>
+        <v>1.296151919397994</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.074475419511248</v>
+        <v>4.085558915810622</v>
       </c>
       <c r="E15" t="n">
-        <v>303.5918450257223</v>
+        <v>284.8419492937152</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04770939544814712</v>
+        <v>-0.04375760389959937</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7948277833348151</v>
+        <v>0.7948283709903038</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06002482103478497</v>
+        <v>-0.05505289631908871</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.717668043402535</v>
+        <v>0.7176566576138841</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137566803650502</v>
+        <v>1.137602680286492</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.915281501056894</v>
+        <v>3.950559650357936</v>
       </c>
       <c r="E16" t="n">
-        <v>199.4990177172872</v>
+        <v>196.9987744148829</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4166931326974341</v>
+        <v>0.4396700656303327</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9622633377977453</v>
+        <v>0.9620998581174198</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4330344057907123</v>
+        <v>0.456990053496789</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5159809085634119</v>
+        <v>0.515893895561667</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9901656012182042</v>
+        <v>0.9898766217533107</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.324512369535344</v>
+        <v>3.336742633691085</v>
       </c>
       <c r="E17" t="n">
-        <v>107.7769525415004</v>
+        <v>104.4976154161799</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2286794815264216</v>
+        <v>-0.2229950642893322</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573569430496023</v>
+        <v>0.7573419051394409</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3019441276996974</v>
+        <v>-0.2944443754875476</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244709221879923</v>
+        <v>0.7244243037997242</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094212904957354</v>
+        <v>1.094171825778877</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.119691399625707</v>
+        <v>3.123732879956058</v>
       </c>
       <c r="E18" t="n">
-        <v>76.41722330837844</v>
+        <v>74.66476406700562</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4699601090997502</v>
+        <v>-0.4681075203984164</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498552626498134</v>
+        <v>0.7498629925580135</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.626734427973501</v>
+        <v>-0.6242573977434965</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644995772104208</v>
+        <v>0.7644990335447212</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143233535792099</v>
+        <v>1.143297856660061</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.931446195626162</v>
+        <v>2.943736357253884</v>
       </c>
       <c r="E19" t="n">
-        <v>106.7525732763789</v>
+        <v>106.0196767520469</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09716684696747246</v>
+        <v>0.1074850033486989</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837946706531797</v>
+        <v>0.483729946089121</v>
       </c>
       <c r="H19" t="n">
-        <v>0.200843152811679</v>
+        <v>0.2222004327366911</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7180007076357189</v>
+        <v>0.7179259545638137</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6927335387059551</v>
+        <v>0.692601066729443</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.565536809819419</v>
+        <v>2.571292215403374</v>
       </c>
       <c r="E20" t="n">
-        <v>141.4008460330726</v>
+        <v>138.290019809896</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3326262885978836</v>
+        <v>-0.32908369684355</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825575736175814</v>
+        <v>0.7825501210021458</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4250502452621214</v>
+        <v>-0.4205273093845034</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328352676965615</v>
+        <v>0.7328103969495808</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143675776729498</v>
+        <v>1.143679438295377</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>565.9273607147156</v>
+        <v>565.8272430800012</v>
       </c>
       <c r="E2" t="n">
-        <v>15041.57739948019</v>
+        <v>14895.48414629972</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6172580344639913</v>
+        <v>0.6151315059507247</v>
       </c>
       <c r="G2" t="n">
-        <v>0.50141748255897</v>
+        <v>0.5014275245915416</v>
       </c>
       <c r="H2" t="n">
-        <v>1.231026152725733</v>
+        <v>1.226760550194777</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.352025853045</v>
+        <v>222.5749080692823</v>
       </c>
       <c r="E3" t="n">
-        <v>6152.307455230985</v>
+        <v>6097.339033564593</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2494079416178669</v>
+        <v>0.2501462322217296</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010521337214025</v>
+        <v>0.6010517317406792</v>
       </c>
       <c r="H3" t="n">
-        <v>0.41495226058622</v>
+        <v>0.4161808693193383</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907232543373431</v>
+        <v>0.890700269047804</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067715289547704</v>
+        <v>1.067665640431622</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.75130642264449</v>
+        <v>36.76260632513963</v>
       </c>
       <c r="E4" t="n">
-        <v>453.057659487099</v>
+        <v>456.9269777714063</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3449981649042384</v>
+        <v>-0.3468706974595814</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5644381953194144</v>
+        <v>0.564437756074965</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6112239883217057</v>
+        <v>-0.6145419822225929</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7366377715099039</v>
+        <v>0.736661962402674</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8292221727754897</v>
+        <v>0.8292321515119305</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.65764044615386</v>
+        <v>36.55680701352967</v>
       </c>
       <c r="E5" t="n">
-        <v>2239.129445068542</v>
+        <v>2262.274882863484</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7377954523407302</v>
+        <v>0.736087323179168</v>
       </c>
       <c r="G5" t="n">
-        <v>1.114773561643499</v>
+        <v>1.114784756093563</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6618343650463022</v>
+        <v>0.6602954688388193</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,45 +706,45 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4736169276290457</v>
+        <v>0.4736394726921185</v>
       </c>
       <c r="N5" t="n">
-        <v>1.052966136268671</v>
+        <v>1.053005744891001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Dogecoin</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.65602045265007</v>
+        <v>10.74079206951347</v>
       </c>
       <c r="E6" t="n">
-        <v>239.8459954474154</v>
+        <v>1598.685765153004</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3240178842757802</v>
+        <v>-0.498698309731771</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7182283768227099</v>
+        <v>0.8088093941729085</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4511348962695774</v>
+        <v>-0.6165832312590059</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4277673545966229</v>
+        <v>0.5751178664414889</v>
       </c>
       <c r="J6" t="n">
         <v>267</v>
@@ -760,45 +760,45 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7511562613085908</v>
+        <v>0.6760286396727877</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075953194823907</v>
+        <v>1.090443359571622</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dogecoin</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.64375460053239</v>
+        <v>10.63339496728441</v>
       </c>
       <c r="E7" t="n">
-        <v>1520.684739337585</v>
+        <v>240.3076816098486</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.50557884372077</v>
+        <v>-0.3282630103319538</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8083319759587526</v>
+        <v>0.7182675582984206</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6254594136537889</v>
+        <v>-0.4570205162956413</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5751178664414889</v>
+        <v>0.4277673545966229</v>
       </c>
       <c r="J7" t="n">
         <v>267</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6766638461877814</v>
+        <v>0.7511833645205179</v>
       </c>
       <c r="N7" t="n">
-        <v>1.090845538646514</v>
+        <v>1.076029165945882</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.439518614824522</v>
+        <v>9.456363255096521</v>
       </c>
       <c r="E8" t="n">
-        <v>480.6385457910034</v>
+        <v>485.015818459565</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3633912599882285</v>
+        <v>-0.3641349641282734</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174295296711044</v>
+        <v>1.174295186368927</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3094547521445513</v>
+        <v>-0.3100881008072817</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395155030514716</v>
+        <v>0.7395081357765202</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731909251840086</v>
+        <v>1.731857150902152</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.285672071831782</v>
+        <v>7.290424414979644</v>
       </c>
       <c r="E9" t="n">
-        <v>222.4360916693339</v>
+        <v>219.4367834420377</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4094462660043718</v>
+        <v>0.4073137424844127</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824446556581781</v>
+        <v>0.4824571225689831</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8486906450352989</v>
+        <v>0.8442485838234749</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788923182142826</v>
+        <v>0.6789067357383743</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532041304550096</v>
+        <v>0.6532218000674197</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.762663511756775</v>
+        <v>6.770376217232529</v>
       </c>
       <c r="E10" t="n">
-        <v>268.4153121637377</v>
+        <v>267.3572369380981</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2564562788909202</v>
+        <v>-0.2572953878951936</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9628760684818052</v>
+        <v>0.9628791067201521</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2663440158973753</v>
+        <v>-0.2672146337992699</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7139756418246304</v>
+        <v>0.7139751008361186</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371053229902135</v>
+        <v>1.371029059231482</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.560510720949376</v>
+        <v>6.544230458817976</v>
       </c>
       <c r="E11" t="n">
-        <v>543.5792575364828</v>
+        <v>547.7533353907022</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9443212861846522</v>
+        <v>0.9330410850347077</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258946976991463</v>
+        <v>0.8259028228795454</v>
       </c>
       <c r="H11" t="n">
-        <v>1.143391874067517</v>
+        <v>1.129722600755402</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6642864592158219</v>
+        <v>0.6643242424836289</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094159425035932</v>
+        <v>1.094210509527741</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.314355084637901</v>
+        <v>6.324013836182951</v>
       </c>
       <c r="E12" t="n">
-        <v>138.298416441444</v>
+        <v>138.8489563658559</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2752499946916865</v>
+        <v>-0.2743028174054144</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6619129772334166</v>
+        <v>0.6619227434849344</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4158401544597947</v>
+        <v>-0.4144030706079789</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890115980400277</v>
+        <v>0.7889495056769996</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041561242071271</v>
+        <v>1.041473783662357</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.611738024079757</v>
+        <v>4.60867496051829</v>
       </c>
       <c r="E13" t="n">
-        <v>252.6724118283832</v>
+        <v>251.3430200026665</v>
       </c>
       <c r="F13" t="n">
-        <v>1.687323683736155</v>
+        <v>1.678027545886724</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8653516565803235</v>
+        <v>0.865394156745828</v>
       </c>
       <c r="H13" t="n">
-        <v>1.949870519002739</v>
+        <v>1.939032674078446</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6040791817622474</v>
+        <v>0.6041001691461908</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042526315548181</v>
+        <v>1.042592859046052</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.536024385818279</v>
+        <v>4.557367631177114</v>
       </c>
       <c r="E14" t="n">
-        <v>132.6362651365112</v>
+        <v>135.0346530469182</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4079318557957841</v>
+        <v>-0.4060831788311279</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8547410608835163</v>
+        <v>0.8547550557685566</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4772578204843921</v>
+        <v>-0.4750871914597761</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7603627135529519</v>
+        <v>0.760295329914545</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296151919397994</v>
+        <v>1.296032318231943</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.085558915810622</v>
+        <v>4.096860831414648</v>
       </c>
       <c r="E15" t="n">
-        <v>284.8419492937152</v>
+        <v>272.4930401195651</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04375760389959937</v>
+        <v>-0.04117798304860687</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7948283709903038</v>
+        <v>0.7948371553127612</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05505289631908871</v>
+        <v>-0.05180681699813556</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7176566576138841</v>
+        <v>0.7175998329448192</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137602680286492</v>
+        <v>1.137502394459489</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.950559650357936</v>
+        <v>3.938940619860643</v>
       </c>
       <c r="E16" t="n">
-        <v>196.9987744148829</v>
+        <v>200.0000711631706</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4396700656303327</v>
+        <v>0.4274934425204162</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9620998581174198</v>
+        <v>0.9621626129211651</v>
       </c>
       <c r="H16" t="n">
-        <v>0.456990053496789</v>
+        <v>0.4443047742444789</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.515893895561667</v>
+        <v>0.5159365363266233</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9898766217533107</v>
+        <v>0.9900031840052947</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.336742633691085</v>
+        <v>3.342153923735799</v>
       </c>
       <c r="E17" t="n">
-        <v>104.4976154161799</v>
+        <v>103.4174835551198</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2229950642893322</v>
+        <v>-0.2240961483787548</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573419051394409</v>
+        <v>0.7573408190005601</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2944443754875476</v>
+        <v>-0.2958986796386966</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244243037997242</v>
+        <v>0.7244231630371332</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094171825778877</v>
+        <v>1.094146620779208</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.123732879956058</v>
+        <v>3.120538727659934</v>
       </c>
       <c r="E18" t="n">
-        <v>74.66476406700562</v>
+        <v>74.19532262326014</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4681075203984164</v>
+        <v>-0.4705235958188421</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498629925580135</v>
+        <v>0.7498552383393583</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6242573977434965</v>
+        <v>-0.6274859089614034</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644990335447212</v>
+        <v>0.7645336266758301</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143297856660061</v>
+        <v>1.143314869514702</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.943736357253884</v>
+        <v>2.954235457560405</v>
       </c>
       <c r="E19" t="n">
-        <v>106.0196767520469</v>
+        <v>106.6174407150348</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1074850033486989</v>
+        <v>0.109363815083555</v>
       </c>
       <c r="G19" t="n">
-        <v>0.483729946089121</v>
+        <v>0.4837321389661415</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2222004327366911</v>
+        <v>0.2260834173997478</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7179259545638137</v>
+        <v>0.7178781036098661</v>
       </c>
       <c r="N19" t="n">
-        <v>0.692601066729443</v>
+        <v>0.6925441734755855</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.571292215403374</v>
+        <v>2.569565198463861</v>
       </c>
       <c r="E20" t="n">
-        <v>138.290019809896</v>
+        <v>137.9653470058203</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.32908369684355</v>
+        <v>-0.331614633457435</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825501210021458</v>
+        <v>0.7825528147060347</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4205273093845034</v>
+        <v>-0.423760067340638</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328103969495808</v>
+        <v>0.7328319775761725</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143679438295377</v>
+        <v>1.143694150467657</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>565.8272430800012</v>
+        <v>565.4040901169689</v>
       </c>
       <c r="E2" t="n">
-        <v>14895.48414629972</v>
+        <v>14619.43469211362</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6151315059507247</v>
+        <v>0.6144820096700621</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014275245915416</v>
+        <v>0.5014310868928045</v>
       </c>
       <c r="H2" t="n">
-        <v>1.226760550194777</v>
+        <v>1.22545654972809</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.5749080692823</v>
+        <v>222.3195392524874</v>
       </c>
       <c r="E3" t="n">
-        <v>6097.339033564593</v>
+        <v>5986.391974917486</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2501462322217296</v>
+        <v>0.2478763622868565</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010517317406792</v>
+        <v>0.6010543061129033</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4161808693193383</v>
+        <v>0.4124026061636681</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.890700269047804</v>
+        <v>0.8907181210942889</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067665640431622</v>
+        <v>1.067684027199071</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.76260632513963</v>
+        <v>36.62566064219715</v>
       </c>
       <c r="E4" t="n">
-        <v>456.9269777714063</v>
+        <v>446.9170691769207</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3468706974595814</v>
+        <v>-0.349489822870822</v>
       </c>
       <c r="G4" t="n">
-        <v>0.564437756074965</v>
+        <v>0.5644547197969308</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6145419822225929</v>
+        <v>-0.6191636115587004</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.736661962402674</v>
+        <v>0.7367010064942534</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8292321515119305</v>
+        <v>0.8292951335977448</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.55680701352967</v>
+        <v>36.51884487950979</v>
       </c>
       <c r="E5" t="n">
-        <v>2262.274882863484</v>
+        <v>2235.759709615556</v>
       </c>
       <c r="F5" t="n">
-        <v>0.736087323179168</v>
+        <v>0.7347211446436936</v>
       </c>
       <c r="G5" t="n">
-        <v>1.114784756093563</v>
+        <v>1.114794153215526</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6602954688388193</v>
+        <v>0.659064404423413</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4736394726921185</v>
+        <v>0.4736479712722052</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053005744891001</v>
+        <v>1.0530260346015</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.74079206951347</v>
+        <v>10.81960887402536</v>
       </c>
       <c r="E6" t="n">
-        <v>1598.685765153004</v>
+        <v>1665.325226705665</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.498698309731771</v>
+        <v>-0.4945757070593607</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8088093941729085</v>
+        <v>0.8091800943724317</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6165832312590059</v>
+        <v>-0.6112059731807098</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6760286396727877</v>
+        <v>0.6755861353157711</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090443359571622</v>
+        <v>1.090221302630143</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.63339496728441</v>
+        <v>10.62372289708547</v>
       </c>
       <c r="E7" t="n">
-        <v>240.3076816098486</v>
+        <v>238.6579782533351</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3282630103319538</v>
+        <v>-0.3285659587103531</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182675582984206</v>
+        <v>0.7182718673578719</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4570205162956413</v>
+        <v>-0.4574395485082369</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511833645205179</v>
+        <v>0.7511867557009553</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076029165945882</v>
+        <v>1.076032834532201</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.456363255096521</v>
+        <v>9.409315455033102</v>
       </c>
       <c r="E8" t="n">
-        <v>485.015818459565</v>
+        <v>480.8582290348747</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3641349641282734</v>
+        <v>-0.3693343488327411</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174295186368927</v>
+        <v>1.1743179596132</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3100881008072817</v>
+        <v>-0.3145096656397843</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395081357765202</v>
+        <v>0.7395527054944285</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731857150902152</v>
+        <v>1.731982812482265</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.290424414979644</v>
+        <v>7.274838722682576</v>
       </c>
       <c r="E9" t="n">
-        <v>219.4367834420377</v>
+        <v>215.0992197233502</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4073137424844127</v>
+        <v>0.4037614641809875</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824571225689831</v>
+        <v>0.4824854767513532</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8442485838234749</v>
+        <v>0.8368365135041447</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6789067357383743</v>
+        <v>0.678917355160396</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532218000674197</v>
+        <v>0.653265767404163</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.770376217232529</v>
+        <v>6.768117617636237</v>
       </c>
       <c r="E10" t="n">
-        <v>267.3572369380981</v>
+        <v>254.2366141251317</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2572953878951936</v>
+        <v>-0.2582740267796877</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9628791067201521</v>
+        <v>0.9628838534904324</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2672146337992699</v>
+        <v>-0.2682296788376398</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7139751008361186</v>
+        <v>0.7139815222795627</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371029059231482</v>
+        <v>1.371038408794306</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.544230458817976</v>
+        <v>6.537435783591282</v>
       </c>
       <c r="E11" t="n">
-        <v>547.7533353907022</v>
+        <v>530.7191961799493</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9330410850347077</v>
+        <v>0.9280003893828128</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8259028228795454</v>
+        <v>0.825916062732876</v>
       </c>
       <c r="H11" t="n">
-        <v>1.129722600755402</v>
+        <v>1.123601333423822</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643242424836289</v>
+        <v>0.6643409723294698</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094210509527741</v>
+        <v>1.094247832894702</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.324013836182951</v>
+        <v>6.29627645610381</v>
       </c>
       <c r="E12" t="n">
-        <v>138.8489563658559</v>
+        <v>135.2985389475213</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2743028174054144</v>
+        <v>-0.2794136249987806</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6619227434849344</v>
+        <v>0.661892301657825</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4144030706079789</v>
+        <v>-0.4221436392279233</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7889495056769996</v>
+        <v>0.7890718342837073</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041473783662357</v>
+        <v>1.041579962271182</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.60867496051829</v>
+        <v>4.608328454512141</v>
       </c>
       <c r="E13" t="n">
-        <v>251.3430200026665</v>
+        <v>241.1729550378872</v>
       </c>
       <c r="F13" t="n">
-        <v>1.678027545886724</v>
+        <v>1.674930756147743</v>
       </c>
       <c r="G13" t="n">
-        <v>0.865394156745828</v>
+        <v>0.8654105160466383</v>
       </c>
       <c r="H13" t="n">
-        <v>1.939032674078446</v>
+        <v>1.935417614058064</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6041001691461908</v>
+        <v>0.604107637779659</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042592859046052</v>
+        <v>1.042618051063065</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.557367631177114</v>
+        <v>4.568676476667498</v>
       </c>
       <c r="E14" t="n">
-        <v>135.0346530469182</v>
+        <v>132.7807440593579</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4060831788311279</v>
+        <v>-0.4042329555684621</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8547550557685566</v>
+        <v>0.8547773103756019</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4750871914597761</v>
+        <v>-0.4729102547081369</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.760295329914545</v>
+        <v>0.7602319385351317</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296032318231943</v>
+        <v>1.295948792703412</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.096860831414648</v>
+        <v>4.090568280354807</v>
       </c>
       <c r="E15" t="n">
-        <v>272.4930401195651</v>
+        <v>262.8037582815239</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04117798304860687</v>
+        <v>-0.0446170627251482</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7948371553127612</v>
+        <v>0.7948269167455809</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05180681699813556</v>
+        <v>-0.0561343127480292</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7175998329448192</v>
+        <v>0.7176419811582837</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137502394459489</v>
+        <v>1.137546470734011</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.938940619860643</v>
+        <v>3.898912878188745</v>
       </c>
       <c r="E16" t="n">
-        <v>200.0000711631706</v>
+        <v>195.0383716093806</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4274934425204162</v>
+        <v>0.4113012461601753</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9621626129211651</v>
+        <v>0.9623295583386999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4443047742444789</v>
+        <v>0.4274016552813962</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5159365363266233</v>
+        <v>0.515959205765205</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9900031840052947</v>
+        <v>0.9902114320067322</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.342153923735799</v>
+        <v>3.32340714175523</v>
       </c>
       <c r="E17" t="n">
-        <v>103.4174835551198</v>
+        <v>99.73705136575484</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2240961483787548</v>
+        <v>-0.2310599307573213</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573408190005601</v>
+        <v>0.757378489462981</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2958986796386966</v>
+        <v>-0.3050785491956001</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244231630371332</v>
+        <v>0.7244907356710624</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094146620779208</v>
+        <v>1.094295334604527</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.120538727659934</v>
+        <v>3.111953560011091</v>
       </c>
       <c r="E18" t="n">
-        <v>74.19532262326014</v>
+        <v>72.6025068712442</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4705235958188421</v>
+        <v>-0.4726151366007169</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498552383393583</v>
+        <v>0.7498646606812652</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6274859089614034</v>
+        <v>-0.6302672487210395</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645336266758301</v>
+        <v>0.7645672494939814</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143314869514702</v>
+        <v>1.143371394586823</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.954235457560405</v>
+        <v>2.949608641177287</v>
       </c>
       <c r="E19" t="n">
-        <v>106.6174407150348</v>
+        <v>105.8788976449332</v>
       </c>
       <c r="F19" t="n">
-        <v>0.109363815083555</v>
+        <v>0.106545918210583</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837321389661415</v>
+        <v>0.483730460621527</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2260834173997478</v>
+        <v>0.2202588567064521</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7178781036098661</v>
+        <v>0.7179217093781377</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6925441734755855</v>
+        <v>0.6925789171143314</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.569565198463861</v>
+        <v>2.562716716816062</v>
       </c>
       <c r="E20" t="n">
-        <v>137.9653470058203</v>
+        <v>134.6038193655455</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.331614633457435</v>
+        <v>-0.3341429995089016</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825528147060347</v>
+        <v>0.7825686562674999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.423760067340638</v>
+        <v>-0.4269823444023598</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328319775761725</v>
+        <v>0.7328581525341237</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143694150467657</v>
+        <v>1.143750027979251</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>565.4040901169689</v>
+        <v>565.7604697129295</v>
       </c>
       <c r="E2" t="n">
-        <v>14619.43469211362</v>
+        <v>14538.49182727542</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6144820096700621</v>
+        <v>0.6163980736160199</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014310868928045</v>
+        <v>0.5014212444587431</v>
       </c>
       <c r="H2" t="n">
-        <v>1.22545654972809</v>
+        <v>1.229301870289497</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.3195392524874</v>
+        <v>222.4464202147283</v>
       </c>
       <c r="E3" t="n">
-        <v>5986.391974917486</v>
+        <v>5954.766831058489</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2478763622868565</v>
+        <v>0.2494448533668305</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010543061129033</v>
+        <v>0.6010521036596225</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4124026061636681</v>
+        <v>0.4150136932356398</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907181210942889</v>
+        <v>0.8907173445368574</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067684027199071</v>
+        <v>1.067700141580341</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.62566064219715</v>
+        <v>36.60398768925627</v>
       </c>
       <c r="E4" t="n">
-        <v>446.9170691769207</v>
+        <v>448.0727003052599</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.349489822870822</v>
+        <v>-0.3487417896949202</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5644547197969308</v>
+        <v>0.5644477803837999</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6191636115587004</v>
+        <v>-0.617845975862977</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7367010064942534</v>
+        <v>0.7366933497356186</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8292951335977448</v>
+        <v>0.8292925971468093</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.51884487950979</v>
+        <v>36.49985511967314</v>
       </c>
       <c r="E5" t="n">
-        <v>2235.759709615556</v>
+        <v>2234.639877698685</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7347211446436936</v>
+        <v>0.7330138276392557</v>
       </c>
       <c r="G5" t="n">
-        <v>1.114794153215526</v>
+        <v>1.114806451554086</v>
       </c>
       <c r="H5" t="n">
-        <v>0.659064404423413</v>
+        <v>0.6575256418882437</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4736479712722052</v>
+        <v>0.4736295028445683</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0530260346015</v>
+        <v>1.053017260940812</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.81960887402536</v>
+        <v>10.85337181057946</v>
       </c>
       <c r="E6" t="n">
-        <v>1665.325226705665</v>
+        <v>1703.142990061687</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4945757070593607</v>
+        <v>-0.4886448721787831</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8091800943724317</v>
+        <v>0.8098234497960745</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6112059731807098</v>
+        <v>-0.6033967925994623</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6755861353157711</v>
+        <v>0.6750625403473516</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090221302630143</v>
+        <v>1.09026388748707</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.62372289708547</v>
+        <v>10.63500264347642</v>
       </c>
       <c r="E7" t="n">
-        <v>238.6579782533351</v>
+        <v>238.3201595950104</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3285659587103531</v>
+        <v>-0.3252315099714523</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182718673578719</v>
+        <v>0.7182355436549174</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4574395485082369</v>
+        <v>-0.4528201268297475</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511867557009553</v>
+        <v>0.7511650383699056</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076032834532201</v>
+        <v>1.075968431075455</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.409315455033102</v>
+        <v>9.405547113671659</v>
       </c>
       <c r="E8" t="n">
-        <v>480.8582290348747</v>
+        <v>481.4500847253365</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3693343488327411</v>
+        <v>-0.3674787417307129</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1743179596132</v>
+        <v>1.174305096216735</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3145096656397843</v>
+        <v>-0.3129329361804024</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395527054944285</v>
+        <v>0.739544225560038</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731982812482265</v>
+        <v>1.731977977698683</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.274838722682576</v>
+        <v>7.278067609181564</v>
       </c>
       <c r="E9" t="n">
-        <v>215.0992197233502</v>
+        <v>208.8260485553413</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4037614641809875</v>
+        <v>0.4061293819020828</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824854767513532</v>
+        <v>0.4824655217928159</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8368365135041447</v>
+        <v>0.8417790775865762</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.678917355160396</v>
+        <v>0.6789017685134556</v>
       </c>
       <c r="N9" t="n">
-        <v>0.653265767404163</v>
+        <v>0.6532365742609862</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.768117617636237</v>
+        <v>6.755562927533464</v>
       </c>
       <c r="E10" t="n">
-        <v>254.2366141251317</v>
+        <v>248.7316583193975</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2582740267796877</v>
+        <v>-0.2579944510240437</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9628838534904324</v>
+        <v>0.962882365165925</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2682296788376398</v>
+        <v>-0.2679397404682823</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7139815222795627</v>
+        <v>0.7139840454915977</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371038408794306</v>
+        <v>1.371068047098373</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.537435783591282</v>
+        <v>6.541915640357855</v>
       </c>
       <c r="E11" t="n">
-        <v>530.7191961799493</v>
+        <v>530.3303355771822</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9280003893828128</v>
+        <v>0.935414399390514</v>
       </c>
       <c r="G11" t="n">
-        <v>0.825916062732876</v>
+        <v>0.8258986468513215</v>
       </c>
       <c r="H11" t="n">
-        <v>1.123601333423822</v>
+        <v>1.132601927556987</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643409723294698</v>
+        <v>0.6643186836075697</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094247832894702</v>
+        <v>1.094209525290041</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.29627645610381</v>
+        <v>6.292688373850973</v>
       </c>
       <c r="E12" t="n">
-        <v>135.2985389475213</v>
+        <v>134.9328306228445</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2794136249987806</v>
+        <v>-0.2788462366139599</v>
       </c>
       <c r="G12" t="n">
-        <v>0.661892301657825</v>
+        <v>0.6618929814614029</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4221436392279233</v>
+        <v>-0.4212859849311159</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890718342837073</v>
+        <v>0.7890786538755148</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041579962271182</v>
+        <v>1.041610479398402</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.608328454512141</v>
+        <v>4.582937546479418</v>
       </c>
       <c r="E13" t="n">
-        <v>241.1729550378872</v>
+        <v>245.5464178389411</v>
       </c>
       <c r="F13" t="n">
-        <v>1.674930756147743</v>
+        <v>1.673382722107439</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8654105160466383</v>
+        <v>0.865419106772095</v>
       </c>
       <c r="H13" t="n">
-        <v>1.935417614058064</v>
+        <v>1.933609633774955</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.604107637779659</v>
+        <v>0.6040836638694743</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042618051063065</v>
+        <v>1.04260748936925</v>
       </c>
     </row>
     <row r="14">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.568676476667498</v>
+        <v>4.56188929259534</v>
       </c>
       <c r="E14" t="n">
-        <v>132.7807440593579</v>
+        <v>132.7884598582763</v>
       </c>
       <c r="F14" t="n">
         <v>-0.4042329555684621</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602319385351317</v>
+        <v>0.7602667611350538</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295948792703412</v>
+        <v>1.296033593376121</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.090568280354807</v>
+        <v>4.08707540702992</v>
       </c>
       <c r="E15" t="n">
-        <v>262.8037582815239</v>
+        <v>256.7984794609856</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0446170627251482</v>
+        <v>-0.04444518756044313</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7948269167455809</v>
+        <v>0.7948271486394389</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0561343127480292</v>
+        <v>-0.05591805417885267</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7176419811582837</v>
+        <v>0.7176570083826751</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137546470734011</v>
+        <v>1.137592951989184</v>
       </c>
     </row>
     <row r="16">
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.898912878188745</v>
+        <v>3.893182251203504</v>
       </c>
       <c r="E16" t="n">
-        <v>195.0383716093806</v>
+        <v>194.2156293522882</v>
       </c>
       <c r="F16" t="n">
         <v>0.4113012461601753</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.515959205765205</v>
+        <v>0.5159244107758522</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9902114320067322</v>
+        <v>0.9901640902630936</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.32340714175523</v>
+        <v>3.318078044436201</v>
       </c>
       <c r="E17" t="n">
-        <v>99.73705136575484</v>
+        <v>98.34614575274118</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2310599307573213</v>
+        <v>-0.2308768894299001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.757378489462981</v>
+        <v>0.7573765123445865</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3050785491956001</v>
+        <v>-0.3048376674834843</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244907356710624</v>
+        <v>0.7244845264454177</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094295334604527</v>
+        <v>1.094304579135154</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.111953560011091</v>
+        <v>3.112482248626885</v>
       </c>
       <c r="E18" t="n">
-        <v>72.6025068712442</v>
+        <v>71.9727263450656</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4726151366007169</v>
+        <v>-0.4711673835367207</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498646606812652</v>
+        <v>0.7498565410019934</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6302672487210395</v>
+        <v>-0.6283433667286876</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645672494939814</v>
+        <v>0.7645532082003083</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143371394586823</v>
+        <v>1.143360458793308</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.949608641177287</v>
+        <v>2.946227192080238</v>
       </c>
       <c r="E19" t="n">
-        <v>105.8788976449332</v>
+        <v>106.5049749796452</v>
       </c>
       <c r="F19" t="n">
-        <v>0.106545918210583</v>
+        <v>0.1084243023343314</v>
       </c>
       <c r="G19" t="n">
-        <v>0.483730460621527</v>
+        <v>0.4837305055385679</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2202588567064521</v>
+        <v>0.2241419573355535</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7179217093781377</v>
+        <v>0.7179066089455317</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6925789171143314</v>
+        <v>0.6925780084359284</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.562716716816062</v>
+        <v>2.564992945640757</v>
       </c>
       <c r="E20" t="n">
-        <v>134.6038193655455</v>
+        <v>134.9306447936574</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3341429995089016</v>
+        <v>-0.331614633457435</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825686562674999</v>
+        <v>0.7825528147060347</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4269823444023598</v>
+        <v>-0.423760067340638</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328581525341237</v>
+        <v>0.7328373286719589</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143750027979251</v>
+        <v>1.143716826144726</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>565.7604697129295</v>
+        <v>566.4870073811489</v>
       </c>
       <c r="E2" t="n">
-        <v>14538.49182727542</v>
+        <v>14559.36932344845</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6163980736160199</v>
+        <v>0.6187801548706928</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014212444587431</v>
+        <v>0.5014118190176963</v>
       </c>
       <c r="H2" t="n">
-        <v>1.229301870289497</v>
+        <v>1.234075726581256</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.4464202147283</v>
+        <v>222.7295843216232</v>
       </c>
       <c r="E3" t="n">
-        <v>5954.766831058489</v>
+        <v>5957.900827889861</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2494448533668305</v>
+        <v>0.2515216105569369</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010521036596225</v>
+        <v>0.6010521012723233</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4150136932356398</v>
+        <v>0.4184688981612562</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907173445368574</v>
+        <v>0.8907163542933598</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067700141580341</v>
+        <v>1.06771902073324</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.60398768925627</v>
+        <v>36.59872667305488</v>
       </c>
       <c r="E4" t="n">
-        <v>448.0727003052599</v>
+        <v>449.0009066733139</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3487417896949202</v>
+        <v>-0.349489822870822</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5644477803837999</v>
+        <v>0.5644547197969308</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.617845975862977</v>
+        <v>-0.6191636115587004</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7366933497356186</v>
+        <v>0.7366933587069074</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8292925971468093</v>
+        <v>0.8293183917758657</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.49985511967314</v>
+        <v>36.35111513961666</v>
       </c>
       <c r="E5" t="n">
-        <v>2234.639877698685</v>
+        <v>2257.650914028645</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7330138276392557</v>
+        <v>0.7186902095888859</v>
       </c>
       <c r="G5" t="n">
-        <v>1.114806451554086</v>
+        <v>1.114933966212988</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6575256418882437</v>
+        <v>0.6446033858220381</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4736295028445683</v>
+        <v>0.4735855362400665</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053017260940812</v>
+        <v>1.0530597409843</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.85337181057946</v>
+        <v>10.90002540301537</v>
       </c>
       <c r="E6" t="n">
-        <v>1703.142990061687</v>
+        <v>1756.354989293182</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4886448721787831</v>
+        <v>-0.4900843554017753</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8098234497960745</v>
+        <v>0.8096554330531668</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6033967925994623</v>
+        <v>-0.6052999033844481</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6750625403473516</v>
+        <v>0.6754058093763722</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09026388748707</v>
+        <v>1.09061247129867</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.63500264347642</v>
+        <v>10.63861067593661</v>
       </c>
       <c r="E7" t="n">
-        <v>238.3201595950104</v>
+        <v>239.2422867299329</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3252315099714523</v>
+        <v>-0.3258381031803163</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182355436549174</v>
+        <v>0.71824033546852</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4528201268297475</v>
+        <v>-0.4536616604353844</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511650383699056</v>
+        <v>0.7511664503213278</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075968431075455</v>
+        <v>1.075997858064943</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.405547113671659</v>
+        <v>9.397286967554793</v>
       </c>
       <c r="E8" t="n">
-        <v>481.4500847253365</v>
+        <v>482.826388964357</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3674787417307129</v>
+        <v>-0.3697052945469781</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174305096216735</v>
+        <v>1.174321162954479</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3129329361804024</v>
+        <v>-0.3148246886880885</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.739544225560038</v>
+        <v>0.7395537455274485</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731977977698683</v>
+        <v>1.732056528337405</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.278067609181564</v>
+        <v>7.299273928089624</v>
       </c>
       <c r="E9" t="n">
-        <v>208.8260485553413</v>
+        <v>206.3956545799344</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4061293819020828</v>
+        <v>0.4118167530092043</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824655217928159</v>
+        <v>0.482434802383459</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8417790775865762</v>
+        <v>0.853621569121117</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6789017685134556</v>
+        <v>0.6788818828307751</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532365742609862</v>
+        <v>0.6531881271303194</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.755562927533464</v>
+        <v>6.759739663387047</v>
       </c>
       <c r="E10" t="n">
-        <v>248.7316583193975</v>
+        <v>248.7284221354058</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2579944510240437</v>
+        <v>-0.2582740267796877</v>
       </c>
       <c r="G10" t="n">
-        <v>0.962882365165925</v>
+        <v>0.9628838534904324</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2679397404682823</v>
+        <v>-0.2682296788376398</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7139840454915977</v>
+        <v>0.7139872431342108</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371068047098373</v>
+        <v>1.37110208004055</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.541915640357855</v>
+        <v>6.544690354145041</v>
       </c>
       <c r="E11" t="n">
-        <v>530.3303355771822</v>
+        <v>528.4252217847552</v>
       </c>
       <c r="F11" t="n">
-        <v>0.935414399390514</v>
+        <v>0.932447878630756</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258986468513215</v>
+        <v>0.8259040723381655</v>
       </c>
       <c r="H11" t="n">
-        <v>1.132601927556987</v>
+        <v>1.129002640695258</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643186836075697</v>
+        <v>0.6643283372652721</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094209525290041</v>
+        <v>1.094253183325275</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.292688373850973</v>
+        <v>6.483633523523419</v>
       </c>
       <c r="E12" t="n">
-        <v>134.9328306228445</v>
+        <v>134.6562145746464</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2788462366139599</v>
+        <v>-0.2792245088602159</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6618929814614029</v>
+        <v>0.6618924531841418</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4212859849311159</v>
+        <v>-0.421857822244325</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890786538755148</v>
+        <v>0.7891021515434226</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041610479398402</v>
+        <v>1.041660246304499</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.582937546479418</v>
+        <v>4.590452814754466</v>
       </c>
       <c r="E13" t="n">
-        <v>245.5464178389411</v>
+        <v>245.628394583556</v>
       </c>
       <c r="F13" t="n">
-        <v>1.673382722107439</v>
+        <v>1.667192992979428</v>
       </c>
       <c r="G13" t="n">
-        <v>0.865419106772095</v>
+        <v>0.8654562099808097</v>
       </c>
       <c r="H13" t="n">
-        <v>1.933609633774955</v>
+        <v>1.926374753283468</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6040836638694743</v>
+        <v>0.604038678807697</v>
       </c>
       <c r="N13" t="n">
-        <v>1.04260748936925</v>
+        <v>1.042594142808339</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.56188929259534</v>
+        <v>4.562371852905248</v>
       </c>
       <c r="E14" t="n">
-        <v>132.7884598582763</v>
+        <v>132.4081462686491</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4042329555684621</v>
+        <v>-0.4048498683293701</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8547773103756019</v>
+        <v>0.854768974461261</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4729102547081369</v>
+        <v>-0.4736365970518953</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602667611350538</v>
+        <v>0.7603197288098167</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296033593376121</v>
+        <v>1.296135611902069</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.08707540702992</v>
+        <v>4.085900066859919</v>
       </c>
       <c r="E15" t="n">
-        <v>256.7984794609856</v>
+        <v>253.6663910071719</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04444518756044313</v>
+        <v>-0.04942619436298279</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7948271486394389</v>
+        <v>0.7948323916274748</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05591805417885267</v>
+        <v>-0.06218442389065097</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7176570083826751</v>
+        <v>0.7177049727373288</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137592951989184</v>
+        <v>1.137697872940665</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.893182251203504</v>
+        <v>3.876210555592271</v>
       </c>
       <c r="E16" t="n">
-        <v>194.2156293522882</v>
+        <v>195.8239936922353</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4113012461601753</v>
+        <v>0.4018787456935946</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9623295583386999</v>
+        <v>0.9624708750942197</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4274016552813962</v>
+        <v>0.4175489940454076</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5159244107758522</v>
+        <v>0.5158390868931282</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9901640902630936</v>
+        <v>0.9901643290787888</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.318078044436201</v>
+        <v>3.31881247246596</v>
       </c>
       <c r="E17" t="n">
-        <v>98.34614575274118</v>
+        <v>97.38989221642449</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2308768894299001</v>
+        <v>-0.2310599307573213</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573765123445865</v>
+        <v>0.757378489462981</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3048376674834843</v>
+        <v>-0.3050785491956001</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244845264454177</v>
+        <v>0.7244737434313957</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094304579135154</v>
+        <v>1.094311718719771</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.112482248626885</v>
+        <v>3.108951265224317</v>
       </c>
       <c r="E18" t="n">
-        <v>71.9727263450656</v>
+        <v>71.63023307870759</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4711673835367207</v>
+        <v>-0.4723739184346433</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498565410019934</v>
+        <v>0.7498628084950157</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6283433667286876</v>
+        <v>-0.6299471224379081</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645532082003083</v>
+        <v>0.7645725866216234</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143360458793308</v>
+        <v>1.143420488622656</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.946227192080238</v>
+        <v>2.95823338301025</v>
       </c>
       <c r="E19" t="n">
-        <v>106.5049749796452</v>
+        <v>107.2184056051199</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1084243023343314</v>
+        <v>0.1121836350747856</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837305055385679</v>
+        <v>0.4837434829730636</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2241419573355535</v>
+        <v>0.2319072794227851</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7179066089455317</v>
+        <v>0.7178670736379017</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6925780084359284</v>
+        <v>0.6925714658932354</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.564992945640757</v>
+        <v>2.568208792083711</v>
       </c>
       <c r="E20" t="n">
-        <v>134.9306447936574</v>
+        <v>135.8039262811153</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.331614633457435</v>
+        <v>-0.3311086516355367</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825528147060347</v>
+        <v>0.7825512241227631</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.423760067340638</v>
+        <v>-0.4231143488488031</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328373286719589</v>
+        <v>0.7328402314255944</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143716826144726</v>
+        <v>1.143740531110751</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.4081908734362</v>
+        <v>567.5425874919935</v>
       </c>
       <c r="E2" t="n">
-        <v>14487.97856885979</v>
+        <v>14368.84287476695</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6187239700282643</v>
+        <v>0.6227250310241814</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014120054781958</v>
+        <v>0.5014030530615491</v>
       </c>
       <c r="H2" t="n">
-        <v>1.233963214419225</v>
+        <v>1.241964976523068</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.498589653959</v>
+        <v>223.0682398840046</v>
       </c>
       <c r="E3" t="n">
-        <v>5873.803643489062</v>
+        <v>5802.326896465317</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2501554615952641</v>
+        <v>0.2542643473299968</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010517293704687</v>
+        <v>0.6010571789057212</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4161962263335848</v>
+        <v>0.4230285507826526</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907263358041003</v>
+        <v>0.8907224788513156</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06772992804648</v>
+        <v>1.067754049476366</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.49898832405871</v>
+        <v>36.67188318676319</v>
       </c>
       <c r="E4" t="n">
-        <v>448.2532720463794</v>
+        <v>443.5906135381657</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3513588954402831</v>
+        <v>-0.3476193072991837</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5644793920135099</v>
+        <v>0.5644405101902893</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6224476932399223</v>
+        <v>-0.6158652701628221</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7366887397128469</v>
+        <v>0.7366824203813156</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8293491327550391</v>
+        <v>0.8292996994519779</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>35.97854929984143</v>
+        <v>36.39864695474895</v>
       </c>
       <c r="E5" t="n">
-        <v>2267.119386905597</v>
+        <v>2225.121542635142</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6945492637719426</v>
+        <v>0.7224385473698862</v>
       </c>
       <c r="G5" t="n">
-        <v>1.11524788284229</v>
+        <v>1.114896387979335</v>
       </c>
       <c r="H5" t="n">
-        <v>0.622775684632401</v>
+        <v>0.6479871628961424</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4735202884054951</v>
+        <v>0.4735176995884585</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053210719642538</v>
+        <v>1.052891819648835</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.76900783677005</v>
+        <v>10.82396070675757</v>
       </c>
       <c r="E6" t="n">
-        <v>1523.960808387403</v>
+        <v>1447.465740159267</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4984297208300916</v>
+        <v>-0.4946654251953436</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8088316225314971</v>
+        <v>0.8091713565125093</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.616234216053641</v>
+        <v>-0.6113234498652158</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6762040677464679</v>
+        <v>0.6761136311209491</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090790063465199</v>
+        <v>1.09112176463668</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.62417719017068</v>
+        <v>10.68059533047704</v>
       </c>
       <c r="E7" t="n">
-        <v>237.5636868688968</v>
+        <v>236.0124689947766</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3270508500151204</v>
+        <v>-0.3209812604207763</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182523358101043</v>
+        <v>0.7182245581492136</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4553425498383453</v>
+        <v>-0.4469093360548824</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511674945083183</v>
+        <v>0.7511494645273272</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076016931426834</v>
+        <v>1.075968702164909</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.335325708865337</v>
+        <v>9.413971670340723</v>
       </c>
       <c r="E8" t="n">
-        <v>485.9522354973081</v>
+        <v>480.8993488139279</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3741520672775253</v>
+        <v>-0.3674787417307129</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174375999363961</v>
+        <v>1.174305096216735</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.318596486542781</v>
+        <v>-0.3129329361804024</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395516221930524</v>
+        <v>0.7395438091669905</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732131791630928</v>
+        <v>1.732039840359185</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.293944490783292</v>
+        <v>7.241727622209083</v>
       </c>
       <c r="E9" t="n">
-        <v>203.4765295311724</v>
+        <v>206.08000319475</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4073137424844127</v>
+        <v>0.3858003814042898</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824571225689831</v>
+        <v>0.4827746030353205</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8442485838234749</v>
+        <v>0.7991314766325106</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788862400692017</v>
+        <v>0.6784642789605151</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532222969473873</v>
+        <v>0.6532575359260931</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.727094123645643</v>
+        <v>6.745283508512434</v>
       </c>
       <c r="E10" t="n">
-        <v>248.5274193655382</v>
+        <v>248.8564104829008</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.263441070105524</v>
+        <v>-0.2610682275281369</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9629304493303683</v>
+        <v>0.9629045491928713</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2735826562434739</v>
+        <v>-0.2711257598138572</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7139916946520245</v>
+        <v>0.713971682826164</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371176469326326</v>
+        <v>1.371125638726039</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.552182174152172</v>
+        <v>6.575044954523061</v>
       </c>
       <c r="E11" t="n">
-        <v>526.5719064137226</v>
+        <v>518.9426329226229</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9386789828286282</v>
+        <v>0.9443212861846522</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258950518073335</v>
+        <v>0.8258946976991463</v>
       </c>
       <c r="H11" t="n">
-        <v>1.136559640083187</v>
+        <v>1.143391874067517</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643145692194899</v>
+        <v>0.6643133205626306</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094218147087736</v>
+        <v>1.094235158149786</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.254269463287346</v>
+        <v>6.298878266887113</v>
       </c>
       <c r="E12" t="n">
-        <v>136.4127052927451</v>
+        <v>135.1906192242228</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2854582968705646</v>
+        <v>-0.2792245088602159</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6619270914874815</v>
+        <v>0.6618924531841418</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4312533820440604</v>
+        <v>-0.421857822244325</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7891312032829075</v>
+        <v>0.7891194438888223</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041752723277756</v>
+        <v>1.041701284788074</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.550645714695653</v>
+        <v>4.585868399684716</v>
       </c>
       <c r="E13" t="n">
-        <v>132.1333319608502</v>
+        <v>129.6094970578456</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4054666094443985</v>
+        <v>-0.4005278790422501</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8547615562509481</v>
+        <v>0.8548465959359361</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4743622434574704</v>
+        <v>-0.468537724717414</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603321132655968</v>
+        <v>0.7602848368085205</v>
       </c>
       <c r="N13" t="n">
-        <v>1.296144993143239</v>
+        <v>1.296216488350125</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.538151617824814</v>
+        <v>4.562776717303676</v>
       </c>
       <c r="E14" t="n">
-        <v>248.0864291138977</v>
+        <v>244.6284005929708</v>
       </c>
       <c r="F14" t="n">
-        <v>1.625513345394576</v>
+        <v>1.653280201246492</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8658212916173104</v>
+        <v>0.8655557204484647</v>
       </c>
       <c r="H14" t="n">
-        <v>1.877423622094347</v>
+        <v>1.910079457842285</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6038815510402239</v>
+        <v>0.6039076890556023</v>
       </c>
       <c r="N14" t="n">
-        <v>1.042762237028742</v>
+        <v>1.042506126943595</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.993845881249205</v>
+        <v>4.005515888711048</v>
       </c>
       <c r="E15" t="n">
-        <v>267.151430665462</v>
+        <v>264.7195243132633</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07814344761569325</v>
+        <v>-0.07132748599796934</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7953503888562874</v>
+        <v>0.7951516583759149</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09825034187518712</v>
+        <v>-0.08970299595885223</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7174431645162576</v>
+        <v>0.7174666700002789</v>
       </c>
       <c r="N15" t="n">
-        <v>1.138023608621204</v>
+        <v>1.137796846263193</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.879330489764886</v>
+        <v>3.912941333335614</v>
       </c>
       <c r="E16" t="n">
-        <v>188.5231797151211</v>
+        <v>183.3026475816539</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3965020771265724</v>
+        <v>0.4261421999318473</v>
       </c>
       <c r="G16" t="n">
-        <v>0.962566154845009</v>
+        <v>0.9621728905360435</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4119218976595085</v>
+        <v>0.4428956626437853</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.515810571353855</v>
+        <v>0.5158590022823197</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9902072404967137</v>
+        <v>0.9899132929174459</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.299325474074504</v>
+        <v>3.321273331555258</v>
       </c>
       <c r="E17" t="n">
-        <v>94.26306909018807</v>
+        <v>94.34811230853055</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2367284032949338</v>
+        <v>-0.2305107716862409</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7574662054064607</v>
+        <v>0.7573727179550366</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3125266864782489</v>
+        <v>-0.3043557897208621</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244424604850437</v>
+        <v>0.7244490754351486</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094390791571879</v>
+        <v>1.094285250024155</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.098558903373215</v>
+        <v>3.10984849657773</v>
       </c>
       <c r="E18" t="n">
-        <v>69.5194959864223</v>
+        <v>69.25492954154679</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4755074425048975</v>
+        <v>-0.472052248149852</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7499024519725112</v>
+        <v>0.7498606493417244</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6340923959564917</v>
+        <v>-0.6295199628947721</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645748047759936</v>
+        <v>0.7645679801625845</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143483830769294</v>
+        <v>1.143430297382392</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.959088550379994</v>
+        <v>2.963098752416304</v>
       </c>
       <c r="E19" t="n">
-        <v>106.0525431249897</v>
+        <v>105.8112160260292</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1112434815374956</v>
+        <v>0.1140645823520721</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837386277049979</v>
+        <v>0.4837564151447907</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2299660915343236</v>
+        <v>0.2357892914307544</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7178830499325131</v>
+        <v>0.7178847800377582</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6925796702770287</v>
+        <v>0.6926191724553432</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.558663894553726</v>
+        <v>2.569035690031325</v>
       </c>
       <c r="E20" t="n">
-        <v>135.0763118855277</v>
+        <v>134.186645594072</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3356587833925103</v>
+        <v>-0.331614633457435</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825844718714313</v>
+        <v>0.7825528147060347</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4289106102371717</v>
+        <v>-0.423760067340638</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328558739346166</v>
+        <v>0.7328448089575946</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143813113357809</v>
+        <v>1.143769995995764</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.5425874919935</v>
+        <v>567.4245138381616</v>
       </c>
       <c r="E2" t="n">
-        <v>14368.84287476695</v>
+        <v>12789.27006346857</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6227250310241814</v>
+        <v>0.6224500061503733</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014030530615491</v>
+        <v>0.5014033877409891</v>
       </c>
       <c r="H2" t="n">
-        <v>1.241964976523068</v>
+        <v>1.241415637326953</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.0682398840046</v>
+        <v>223.2540691360425</v>
       </c>
       <c r="E3" t="n">
-        <v>5802.326896465317</v>
+        <v>5189.050946911418</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2542643473299968</v>
+        <v>0.2541904477750323</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010571789057212</v>
+        <v>0.6010569663662927</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4230285507826526</v>
+        <v>0.4229057510334636</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907224788513156</v>
+        <v>0.8907211771312979</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067754049476366</v>
+        <v>1.067751398762607</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.67188318676319</v>
+        <v>36.61926234791151</v>
       </c>
       <c r="E4" t="n">
-        <v>443.5906135381657</v>
+        <v>410.5568708902953</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3476193072991837</v>
+        <v>-0.349489822870822</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5644405101902893</v>
+        <v>0.5644547197969308</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6158652701628221</v>
+        <v>-0.6191636115587004</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7366824203813156</v>
+        <v>0.7366750652031351</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8292996994519779</v>
+        <v>0.8293117431536422</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.39864695474895</v>
+        <v>36.37048211323197</v>
       </c>
       <c r="E5" t="n">
-        <v>2225.121542635142</v>
+        <v>1995.321973996356</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7224385473698862</v>
+        <v>0.7183495603494716</v>
       </c>
       <c r="G5" t="n">
-        <v>1.114896387979335</v>
+        <v>1.114937529548575</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6479871628961424</v>
+        <v>0.6442957935412963</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4735176995884585</v>
+        <v>0.4735100019935781</v>
       </c>
       <c r="N5" t="n">
-        <v>1.052891819648835</v>
+        <v>1.052912853696107</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.82396070675757</v>
+        <v>10.90960244304205</v>
       </c>
       <c r="E6" t="n">
-        <v>1447.465740159267</v>
+        <v>1375.874258556117</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4946654251953436</v>
+        <v>-0.4871142282729889</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8091713565125093</v>
+        <v>0.8100104100258335</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6113234498652158</v>
+        <v>-0.6013678617506328</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6761136311209491</v>
+        <v>0.6753567940918728</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09112176463668</v>
+        <v>1.091029791722665</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.68059533047704</v>
+        <v>10.69086209917648</v>
       </c>
       <c r="E7" t="n">
-        <v>236.0124689947766</v>
+        <v>212.2583391887148</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3209812604207763</v>
+        <v>-0.3215888774764257</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182245581492136</v>
+        <v>0.7182237106189829</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4469093360548824</v>
+        <v>-0.4477558631408485</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511494645273272</v>
+        <v>0.7511519897393439</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075968702164909</v>
+        <v>1.075970331473133</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.413971670340723</v>
+        <v>9.411003613362546</v>
       </c>
       <c r="E8" t="n">
-        <v>480.8993488139279</v>
+        <v>415.4672691388561</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3674787417307129</v>
+        <v>-0.3693343488327411</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174305096216735</v>
+        <v>1.1743179596132</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3129329361804024</v>
+        <v>-0.3145096656397843</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395438091669905</v>
+        <v>0.7395416168745228</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732039840359185</v>
+        <v>1.732052522600338</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.241727622209083</v>
+        <v>7.239942876357148</v>
       </c>
       <c r="E9" t="n">
-        <v>206.08000319475</v>
+        <v>204.4326469168729</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3858003814042898</v>
+        <v>0.3952458421907128</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4827746030353205</v>
+        <v>0.4825921539321007</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7991314766325106</v>
+        <v>0.8190059431557246</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6784642789605151</v>
+        <v>0.6787020848916707</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532575359260931</v>
+        <v>0.6532391065440404</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.745283508512434</v>
+        <v>6.735565570592461</v>
       </c>
       <c r="E10" t="n">
-        <v>248.8564104829008</v>
+        <v>229.537571793733</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2610682275281369</v>
+        <v>-0.2639990881030823</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9629045491928713</v>
+        <v>0.9629376530133745</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2711257598138572</v>
+        <v>-0.274160105046194</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713971682826164</v>
+        <v>0.7139575816784653</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371125638726039</v>
+        <v>1.371144780552833</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.575044954523061</v>
+        <v>6.568548770262284</v>
       </c>
       <c r="E11" t="n">
-        <v>518.9426329226229</v>
+        <v>446.8807844478168</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9443212861846522</v>
+        <v>0.9413511040328191</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258946976991463</v>
+        <v>0.825893959514321</v>
       </c>
       <c r="H11" t="n">
-        <v>1.143391874067517</v>
+        <v>1.139796572173012</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643133205626306</v>
+        <v>0.6643169720893297</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094235158149786</v>
+        <v>1.094239464402744</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.298878266887113</v>
+        <v>6.273124442146165</v>
       </c>
       <c r="E12" t="n">
-        <v>135.1906192242228</v>
+        <v>120.7516828532146</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2792245088602159</v>
+        <v>-0.2831931473210986</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6618924531841418</v>
+        <v>0.6619050367533155</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.421857822244325</v>
+        <v>-0.4278455844816927</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7891194438888223</v>
+        <v>0.7891211169186916</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041701284788074</v>
+        <v>1.041722602334513</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.585868399684716</v>
+        <v>4.584688160146118</v>
       </c>
       <c r="E13" t="n">
-        <v>129.6094970578456</v>
+        <v>114.6205114475784</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4005278790422501</v>
+        <v>-0.402381188233135</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8548465959359361</v>
+        <v>0.8548078240595354</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.468537724717414</v>
+        <v>-0.4707270767857525</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7602848368085205</v>
+        <v>0.7603218422444591</v>
       </c>
       <c r="N13" t="n">
-        <v>1.296216488350125</v>
+        <v>1.296219920814852</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.562776717303676</v>
+        <v>4.572912908351354</v>
       </c>
       <c r="E14" t="n">
-        <v>244.6284005929708</v>
+        <v>220.590939303944</v>
       </c>
       <c r="F14" t="n">
-        <v>1.653280201246492</v>
+        <v>1.654825101936333</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8655557204484647</v>
+        <v>0.8655435679440479</v>
       </c>
       <c r="H14" t="n">
-        <v>1.910079457842285</v>
+        <v>1.91189116668857</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6039076890556023</v>
+        <v>0.6039216268318679</v>
       </c>
       <c r="N14" t="n">
-        <v>1.042506126943595</v>
+        <v>1.042514854161</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.005515888711048</v>
+        <v>4.015861807547948</v>
       </c>
       <c r="E15" t="n">
-        <v>264.7195243132633</v>
+        <v>232.8097343031116</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07132748599796934</v>
+        <v>-0.06825590982650453</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7951516583759149</v>
+        <v>0.7950775960892106</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08970299595885223</v>
+        <v>-0.08584811113058451</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7174666700002789</v>
+        <v>0.7175326977256169</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137796846263193</v>
+        <v>1.137794810269194</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.912941333335614</v>
+        <v>3.889905907038107</v>
       </c>
       <c r="E16" t="n">
-        <v>183.3026475816539</v>
+        <v>168.4865884208191</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4261421999318473</v>
+        <v>0.4018787456935946</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9621728905360435</v>
+        <v>0.9624708750942197</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4428956626437853</v>
+        <v>0.4175489940454076</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158590022823197</v>
+        <v>0.5157395576387757</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9899132929174459</v>
+        <v>0.9899899272673368</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.321273331555258</v>
+        <v>3.313879941499196</v>
       </c>
       <c r="E17" t="n">
-        <v>94.34811230853055</v>
+        <v>84.96138361360565</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2305107716862409</v>
+        <v>-0.2321579330188964</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573727179550366</v>
+        <v>0.7573914710770262</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3043557897208621</v>
+        <v>-0.3065230358202517</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244490754351486</v>
+        <v>0.7244391801887549</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094285250024155</v>
+        <v>1.094296667721022</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.10984849657773</v>
+        <v>3.109588190248024</v>
       </c>
       <c r="E18" t="n">
-        <v>69.25492954154679</v>
+        <v>60.38199672865609</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.472052248149852</v>
+        <v>-0.4722935057983413</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498606493417244</v>
+        <v>0.7498622354464082</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6295199628947721</v>
+        <v>-0.6298403673005021</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645679801625845</v>
+        <v>0.7645682291364134</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143430297382392</v>
+        <v>1.143432325087707</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.963098752416304</v>
+        <v>2.965123394690083</v>
       </c>
       <c r="E19" t="n">
-        <v>105.8112160260292</v>
+        <v>104.1425996206785</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1140645823520721</v>
+        <v>0.1168876025234917</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837564151447907</v>
+        <v>0.4837838667918475</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2357892914307544</v>
+        <v>0.2416112039837486</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7178847800377582</v>
+        <v>0.7178295346934122</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926191724553432</v>
+        <v>0.6926047100638334</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.569035690031325</v>
+        <v>2.566802255295062</v>
       </c>
       <c r="E20" t="n">
-        <v>134.186645594072</v>
+        <v>117.0530154426933</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.331614633457435</v>
+        <v>-0.3321205124569014</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825528147060347</v>
+        <v>0.7825549312057299</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.423760067340638</v>
+        <v>-0.4244053665921997</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328448089575946</v>
+        <v>0.7328451900981375</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143769995995764</v>
+        <v>1.143772920852197</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.4245138381616</v>
+        <v>566.6856641345196</v>
       </c>
       <c r="E2" t="n">
-        <v>12789.27006346857</v>
+        <v>12234.56016559129</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6224500061503733</v>
+        <v>0.6196434932032153</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014033877409891</v>
+        <v>0.5014091715425725</v>
       </c>
       <c r="H2" t="n">
-        <v>1.241415637326953</v>
+        <v>1.235804066560845</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.2540691360425</v>
+        <v>222.8054883445458</v>
       </c>
       <c r="E3" t="n">
-        <v>5189.050946911418</v>
+        <v>4985.035878320901</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2541904477750323</v>
+        <v>0.2513092773339032</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010569663662927</v>
+        <v>0.6010519492566732</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4229057510334636</v>
+        <v>0.4181157346627024</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907211771312979</v>
+        <v>0.8907236381671298</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067751398762607</v>
+        <v>1.067733119684056</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.61926234791151</v>
+        <v>36.56152298848488</v>
       </c>
       <c r="E4" t="n">
-        <v>410.5568708902953</v>
+        <v>402.8456024056832</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.349489822870822</v>
+        <v>-0.3498637528863531</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5644547197969308</v>
+        <v>0.5644588172669761</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6191636115587004</v>
+        <v>-0.6198215745487691</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7366750652031351</v>
+        <v>0.7366893308113462</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8293117431536422</v>
+        <v>0.8293242564424576</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.37048211323197</v>
+        <v>36.19125428593623</v>
       </c>
       <c r="E5" t="n">
-        <v>1995.321973996356</v>
+        <v>1919.161709064661</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7183495603494716</v>
+        <v>0.7098392261592981</v>
       </c>
       <c r="G5" t="n">
-        <v>1.114937529548575</v>
+        <v>1.11503458165182</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6442957935412963</v>
+        <v>0.6366073643274249</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4735100019935781</v>
+        <v>0.4735467494930907</v>
       </c>
       <c r="N5" t="n">
-        <v>1.052912853696107</v>
+        <v>1.053074079377456</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.90960244304205</v>
+        <v>10.91204881703202</v>
       </c>
       <c r="E6" t="n">
-        <v>1375.874258556117</v>
+        <v>1362.036896381871</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4871142282729889</v>
+        <v>-0.4886448721787831</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8100104100258335</v>
+        <v>0.8098234497960745</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6013678617506328</v>
+        <v>-0.6033967925994623</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6753567940918728</v>
+        <v>0.6753117081611563</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091029791722665</v>
+        <v>1.090692568522979</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.69086209917648</v>
+        <v>10.63536365975995</v>
       </c>
       <c r="E7" t="n">
-        <v>212.2583391887148</v>
+        <v>206.2346052584656</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3215888774764257</v>
+        <v>-0.3270508500151204</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182237106189829</v>
+        <v>0.7182523358101043</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4477558631408485</v>
+        <v>-0.4553425498383453</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511519897393439</v>
+        <v>0.7511631402360784</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075970331473133</v>
+        <v>1.076016775658854</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.411003613362546</v>
+        <v>9.359608717309053</v>
       </c>
       <c r="E8" t="n">
-        <v>415.4672691388561</v>
+        <v>399.4647453743045</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3693343488327411</v>
+        <v>-0.3726707491036465</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1743179596132</v>
+        <v>1.174354357325329</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3145096656397843</v>
+        <v>-0.3173409684896381</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395416168745228</v>
+        <v>0.7395490129886231</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732052522600338</v>
+        <v>1.732103549655744</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.239942876357148</v>
+        <v>7.238583770898389</v>
       </c>
       <c r="E9" t="n">
-        <v>204.4326469168729</v>
+        <v>203.3724563638206</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3952458421907128</v>
+        <v>0.3973734431221811</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4825921539321007</v>
+        <v>0.4825603734271217</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8190059431557246</v>
+        <v>0.8234688652531768</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6787020848916707</v>
+        <v>0.678801172736666</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532391065440404</v>
+        <v>0.6532839165881947</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.735565570592461</v>
+        <v>6.713352638112387</v>
       </c>
       <c r="E10" t="n">
-        <v>229.537571793733</v>
+        <v>223.4984211599566</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2639990881030823</v>
+        <v>-0.2660906437870753</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9629376530133745</v>
+        <v>0.9629684310600445</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.274160105046194</v>
+        <v>-0.2763233302405981</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7139575816784653</v>
+        <v>0.7139740269371013</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371144780552833</v>
+        <v>1.37120437271233</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.568548770262284</v>
+        <v>6.548466204331257</v>
       </c>
       <c r="E11" t="n">
-        <v>446.8807844478168</v>
+        <v>429.7199482149956</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9413511040328191</v>
+        <v>0.9348209975044466</v>
       </c>
       <c r="G11" t="n">
-        <v>0.825893959514321</v>
+        <v>0.8258995675867911</v>
       </c>
       <c r="H11" t="n">
-        <v>1.139796572173012</v>
+        <v>1.131882173320316</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643169720893297</v>
+        <v>0.6643241849738233</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094239464402744</v>
+        <v>1.09424615313552</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.273124442146165</v>
+        <v>6.266565689265562</v>
       </c>
       <c r="E12" t="n">
-        <v>120.7516828532146</v>
+        <v>117.3631615791888</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2831931473210986</v>
+        <v>-0.2839484110330769</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6619050367533155</v>
+        <v>0.6619111872487886</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4278455844816927</v>
+        <v>-0.4289826437490788</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7891211169186916</v>
+        <v>0.7891302099644611</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041722602334513</v>
+        <v>1.041732269404875</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.584688160146118</v>
+        <v>4.582374367141024</v>
       </c>
       <c r="E13" t="n">
-        <v>114.6205114475784</v>
+        <v>111.195076153598</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.402381188233135</v>
+        <v>-0.4005278790422501</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8548078240595354</v>
+        <v>0.8548465959359361</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4707270767857525</v>
+        <v>-0.468537724717414</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603218422444591</v>
+        <v>0.7602235688150368</v>
       </c>
       <c r="N13" t="n">
-        <v>1.296219920814852</v>
+        <v>1.296096216095292</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.572912908351354</v>
+        <v>4.553492414013451</v>
       </c>
       <c r="E14" t="n">
-        <v>220.590939303944</v>
+        <v>216.2996039574926</v>
       </c>
       <c r="F14" t="n">
-        <v>1.654825101936333</v>
+        <v>1.637844486574715</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8655435679440479</v>
+        <v>0.8656923084832411</v>
       </c>
       <c r="H14" t="n">
-        <v>1.91189116668857</v>
+        <v>1.891947601387776</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6039216268318679</v>
+        <v>0.6039166527595534</v>
       </c>
       <c r="N14" t="n">
-        <v>1.042514854161</v>
+        <v>1.042673391175695</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.015861807547948</v>
+        <v>4.021527405871925</v>
       </c>
       <c r="E15" t="n">
-        <v>232.8097343031116</v>
+        <v>225.9271965862706</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06825590982650453</v>
+        <v>-0.06586502467188937</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7950775960892106</v>
+        <v>0.7950265886831953</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08584811113058451</v>
+        <v>-0.08284631685209647</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7175326977256169</v>
+        <v>0.7176296650653979</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137794810269194</v>
+        <v>1.137862442363334</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.889905907038107</v>
+        <v>3.868108298603038</v>
       </c>
       <c r="E16" t="n">
-        <v>168.4865884208191</v>
+        <v>166.0611837303291</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4018787456935946</v>
+        <v>0.407260956654893</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624708750942197</v>
+        <v>0.9623861599634363</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4175489940454076</v>
+        <v>0.4231783182234936</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5157395576387757</v>
+        <v>0.5158438575163488</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9899899272673368</v>
+        <v>0.9900915606481563</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.313879941499196</v>
+        <v>3.309703231482044</v>
       </c>
       <c r="E17" t="n">
-        <v>84.96138361360565</v>
+        <v>82.49179242631445</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2321579330188964</v>
+        <v>-0.2336212804649691</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573914710770262</v>
+        <v>0.7574117635055355</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3065230358202517</v>
+        <v>-0.3084468603757851</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244391801887549</v>
+        <v>0.7244567906600419</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094296667721022</v>
+        <v>1.094339965320706</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.109588190248024</v>
+        <v>3.103531447776811</v>
       </c>
       <c r="E18" t="n">
-        <v>60.38199672865609</v>
+        <v>58.5478220247535</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4722935057983413</v>
+        <v>-0.4733386133590767</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498622354464082</v>
+        <v>0.7498714145901196</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6298403673005021</v>
+        <v>-0.6312263731479936</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645682291364134</v>
+        <v>0.7645749025139781</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143432325087707</v>
+        <v>1.143443112427353</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.965123394690083</v>
+        <v>2.957496550711325</v>
       </c>
       <c r="E19" t="n">
-        <v>104.1425996206785</v>
+        <v>103.6765150471556</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1168876025234917</v>
+        <v>0.1121836350747856</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837838667918475</v>
+        <v>0.4837434829730636</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2416112039837486</v>
+        <v>0.2319072794227851</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7178295346934122</v>
+        <v>0.7178776154924794</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926047100638334</v>
+        <v>0.6925852931616047</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.566802255295062</v>
+        <v>2.560072547182231</v>
       </c>
       <c r="E20" t="n">
-        <v>117.0530154426933</v>
+        <v>113.9390993526661</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3321205124569014</v>
+        <v>-0.3341429995089016</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825549312057299</v>
+        <v>0.7825686562674999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4244053665921997</v>
+        <v>-0.4269823444023598</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328451900981375</v>
+        <v>0.7328524670290187</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143772920852197</v>
+        <v>1.143791144866458</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.6856641345196</v>
+        <v>566.3456363879791</v>
       </c>
       <c r="E2" t="n">
-        <v>12234.56016559129</v>
+        <v>11909.33877136832</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6196434932032153</v>
+        <v>0.6179678033727827</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014091715425725</v>
+        <v>0.5014146834510281</v>
       </c>
       <c r="H2" t="n">
-        <v>1.235804066560845</v>
+        <v>1.232448557588238</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.8054883445458</v>
+        <v>222.863668205093</v>
       </c>
       <c r="E3" t="n">
-        <v>4985.035878320901</v>
+        <v>4835.58167584489</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2513092773339032</v>
+        <v>0.2526018901687279</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010519492566732</v>
+        <v>0.6010534113765238</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4181157346627024</v>
+        <v>0.4202652965403236</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907236381671298</v>
+        <v>0.8906995909043167</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067733119684056</v>
+        <v>1.067695153919442</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.56152298848488</v>
+        <v>36.62548690007484</v>
       </c>
       <c r="E4" t="n">
-        <v>402.8456024056832</v>
+        <v>388.6040040758007</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3498637528863531</v>
+        <v>-0.3487417896949202</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5644588172669761</v>
+        <v>0.5644477803837999</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6198215745487691</v>
+        <v>-0.617845975862977</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7366893308113462</v>
+        <v>0.7366926853679898</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8293242564424576</v>
+        <v>0.829302700549166</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.19125428593623</v>
+        <v>36.30166080101724</v>
       </c>
       <c r="E5" t="n">
-        <v>1919.161709064661</v>
+        <v>1817.087978544534</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7098392261592981</v>
+        <v>0.7207344856759166</v>
       </c>
       <c r="G5" t="n">
-        <v>1.11503458165182</v>
+        <v>1.114913101155337</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6366073643274249</v>
+        <v>0.6464490236315728</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4735467494930907</v>
+        <v>0.4736035644872678</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053074079377456</v>
+        <v>1.053074104584519</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.91204881703202</v>
+        <v>10.90557720401946</v>
       </c>
       <c r="E6" t="n">
-        <v>1362.036896381871</v>
+        <v>1208.190557996194</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4886448721787831</v>
+        <v>-0.4914328807971007</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8098234497960745</v>
+        <v>0.8095049194649172</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6033967925994623</v>
+        <v>-0.6070783129050504</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6753117081611563</v>
+        <v>0.6754925752340699</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090692568522979</v>
+        <v>1.090543577524513</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.63536365975995</v>
+        <v>10.63678602754635</v>
       </c>
       <c r="E7" t="n">
-        <v>206.2346052584656</v>
+        <v>198.6095581625326</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3270508500151204</v>
+        <v>-0.3249281584458512</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182523358101043</v>
+        <v>0.7182334498449124</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4553425498383453</v>
+        <v>-0.4523990890650006</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511631402360784</v>
+        <v>0.7511637995490748</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076016775658854</v>
+        <v>1.07597759889183</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.359608717309053</v>
+        <v>9.368249538595991</v>
       </c>
       <c r="E8" t="n">
-        <v>399.4647453743045</v>
+        <v>391.6189126551691</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3726707491036465</v>
+        <v>-0.3711884911846909</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174354357325329</v>
+        <v>1.174336078469819</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3173409684896381</v>
+        <v>-0.3160836986873095</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395490129886231</v>
+        <v>0.7395578851525748</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732103549655744</v>
+        <v>1.73207832820941</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.238583770898389</v>
+        <v>7.244112922393493</v>
       </c>
       <c r="E9" t="n">
-        <v>203.3724563638206</v>
+        <v>200.1970685028725</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3973734431221811</v>
+        <v>0.3961913351432904</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4825603734271217</v>
+        <v>0.4825776086769263</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8234688652531768</v>
+        <v>0.8209898843618554</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.678801172736666</v>
+        <v>0.6788211039878086</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532839165881947</v>
+        <v>0.6533192503004595</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.713352638112387</v>
+        <v>6.723863043486536</v>
       </c>
       <c r="E10" t="n">
-        <v>223.4984211599566</v>
+        <v>219.4122266965932</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2660906437870753</v>
+        <v>-0.263441070105524</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9629684310600445</v>
+        <v>0.9629304493303683</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2763233302405981</v>
+        <v>-0.2735826562434739</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7139740269371013</v>
+        <v>0.7139965454438042</v>
       </c>
       <c r="N10" t="n">
-        <v>1.37120437271233</v>
+        <v>1.37117846169274</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.548466204331257</v>
+        <v>6.56752194446718</v>
       </c>
       <c r="E11" t="n">
-        <v>429.7199482149956</v>
+        <v>406.1817332242671</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9348209975044466</v>
+        <v>0.948481588480597</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258995675867911</v>
+        <v>0.8258991828257187</v>
       </c>
       <c r="H11" t="n">
-        <v>1.131882173320316</v>
+        <v>1.148422965180177</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643241849738233</v>
+        <v>0.6642717751585044</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09424615313552</v>
+        <v>1.094147288431334</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.266565689265562</v>
+        <v>6.280022871703308</v>
       </c>
       <c r="E12" t="n">
-        <v>117.3631615791888</v>
+        <v>114.3697193128175</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2839484110330769</v>
+        <v>-0.281681978832405</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6619111872487886</v>
+        <v>0.6618963391775272</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4289826437490788</v>
+        <v>-0.4255681171804382</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7891302099644611</v>
+        <v>0.7891235997329152</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041732269404875</v>
+        <v>1.041688724045558</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.582374367141024</v>
+        <v>4.59479749581159</v>
       </c>
       <c r="E13" t="n">
-        <v>111.195076153598</v>
+        <v>107.1853072573742</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4005278790422501</v>
+        <v>-0.3992914840863946</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8548465959359361</v>
+        <v>0.854877031193215</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.468537724717414</v>
+        <v>-0.4670747598974252</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7602235688150368</v>
+        <v>0.7601450470984181</v>
       </c>
       <c r="N13" t="n">
-        <v>1.296096216095292</v>
+        <v>1.295994239074153</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.553492414013451</v>
+        <v>4.560453588871018</v>
       </c>
       <c r="E14" t="n">
-        <v>216.2996039574926</v>
+        <v>208.3337803404335</v>
       </c>
       <c r="F14" t="n">
-        <v>1.637844486574715</v>
+        <v>1.647103013950717</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8656923084832411</v>
+        <v>0.8656070694418921</v>
       </c>
       <c r="H14" t="n">
-        <v>1.891947601387776</v>
+        <v>1.902829900653078</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6039166527595534</v>
+        <v>0.6039993927251441</v>
       </c>
       <c r="N14" t="n">
-        <v>1.042673391175695</v>
+        <v>1.0427021017476</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.021527405871925</v>
+        <v>4.025864457416471</v>
       </c>
       <c r="E15" t="n">
-        <v>225.9271965862706</v>
+        <v>221.2912450709976</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06586502467188937</v>
+        <v>-0.06432715874131778</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7950265886831953</v>
+        <v>0.7949968467711925</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08284631685209647</v>
+        <v>-0.08091498601859452</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7176296650653979</v>
+        <v>0.7176755692551174</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137862442363334</v>
+        <v>1.137880148693857</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.868108298603038</v>
+        <v>3.887531383330199</v>
       </c>
       <c r="E16" t="n">
-        <v>166.0611837303291</v>
+        <v>158.1762876546292</v>
       </c>
       <c r="F16" t="n">
-        <v>0.407260956654893</v>
+        <v>0.4086073742419891</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9623861599634363</v>
+        <v>0.9623666322372078</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4231783182234936</v>
+        <v>0.4245859743620808</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158438575163488</v>
+        <v>0.5158863470569953</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9900915606481563</v>
+        <v>0.9901421374766841</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.309703231482044</v>
+        <v>3.318919089301618</v>
       </c>
       <c r="E17" t="n">
-        <v>82.49179242631445</v>
+        <v>80.2301523410262</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2336212804649691</v>
+        <v>-0.2301446071660826</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7574117635055355</v>
+        <v>0.7573691366977897</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3084468603757851</v>
+        <v>-0.3038737598544584</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244567906600419</v>
+        <v>0.7244775378244785</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094339965320706</v>
+        <v>1.094297685106893</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.103531447776811</v>
+        <v>3.111085698748347</v>
       </c>
       <c r="E18" t="n">
-        <v>58.5478220247535</v>
+        <v>57.1299015904814</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4733386133590767</v>
+        <v>-0.4710064563236585</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498714145901196</v>
+        <v>0.7498560822919939</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6312263731479936</v>
+        <v>-0.6281291403064843</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645749025139781</v>
+        <v>0.7645580188263136</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143443112427353</v>
+        <v>1.143381914418989</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.957496550711325</v>
+        <v>2.958998611642519</v>
       </c>
       <c r="E19" t="n">
-        <v>103.6765150471556</v>
+        <v>102.4018192537818</v>
       </c>
       <c r="F19" t="n">
         <v>0.1121836350747856</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7178776154924794</v>
+        <v>0.7178566191230589</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6925852931616047</v>
+        <v>0.6925574233682618</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.560072547182231</v>
+        <v>2.560974912442791</v>
       </c>
       <c r="E20" t="n">
-        <v>113.9390993526661</v>
+        <v>111.207282846813</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3341429995089016</v>
+        <v>-0.3331319618442953</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825686562674999</v>
+        <v>0.7825607419362621</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4269823444023598</v>
+        <v>-0.4256947020112953</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328524670290187</v>
+        <v>0.7328523390500219</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143791144866458</v>
+        <v>1.143766804413342</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.3456363879791</v>
+        <v>566.6965360570954</v>
       </c>
       <c r="E2" t="n">
-        <v>11909.33877136832</v>
+        <v>11718.87310763433</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6179678033727827</v>
+        <v>0.6217366712448582</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014146834510281</v>
+        <v>0.5014044488246898</v>
       </c>
       <c r="H2" t="n">
-        <v>1.232448557588238</v>
+        <v>1.239990336548133</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.863668205093</v>
+        <v>223.001139616082</v>
       </c>
       <c r="E3" t="n">
-        <v>4835.58167584489</v>
+        <v>4750.968996902497</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2526018901687279</v>
+        <v>0.2552251479168652</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010534113765238</v>
+        <v>0.6010603236369989</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4202652965403236</v>
+        <v>0.4246248469246899</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906995909043167</v>
+        <v>0.8907074367133997</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067695153919442</v>
+        <v>1.067738631820603</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.62548690007484</v>
+        <v>36.52548218534151</v>
       </c>
       <c r="E4" t="n">
-        <v>388.6040040758007</v>
+        <v>381.8933319397865</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3487417896949202</v>
+        <v>-0.3513588954402831</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5644477803837999</v>
+        <v>0.5644793920135099</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.617845975862977</v>
+        <v>-0.6224476932399223</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7366926853679898</v>
+        <v>0.7366610984268909</v>
       </c>
       <c r="N4" t="n">
-        <v>0.829302700549166</v>
+        <v>0.8293305133904102</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.30166080101724</v>
+        <v>36.35811221292375</v>
       </c>
       <c r="E5" t="n">
-        <v>1817.087978544534</v>
+        <v>1765.407456155405</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7207344856759166</v>
+        <v>0.7255069992545464</v>
       </c>
       <c r="G5" t="n">
-        <v>1.114913101155337</v>
+        <v>1.1148678492797</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6464490236315728</v>
+        <v>0.650756051242563</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4736035644872678</v>
+        <v>0.4735447030191164</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053074104584519</v>
+        <v>1.052921979113321</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.90557720401946</v>
+        <v>10.8289155861603</v>
       </c>
       <c r="E6" t="n">
-        <v>1208.190557996194</v>
+        <v>1153.423085865178</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4914328807971007</v>
+        <v>-0.4935885254114493</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8095049194649172</v>
+        <v>0.8092782018439753</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6070783129050504</v>
+        <v>-0.6099120479048942</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6754925752340699</v>
+        <v>0.675957480099592</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090543577524513</v>
+        <v>1.091010770447407</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.63678602754635</v>
+        <v>10.61576852379737</v>
       </c>
       <c r="E7" t="n">
-        <v>198.6095581625326</v>
+        <v>197.716454593334</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3249281584458512</v>
+        <v>-0.3276570035188717</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182334498449124</v>
+        <v>0.7182595442977088</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4523990890650006</v>
+        <v>-0.4561818998719248</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511637995490748</v>
+        <v>0.7511465068251849</v>
       </c>
       <c r="N7" t="n">
-        <v>1.07597759889183</v>
+        <v>1.076013882520833</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.368249538595991</v>
+        <v>9.291406613573454</v>
       </c>
       <c r="E8" t="n">
-        <v>391.6189126551691</v>
+        <v>396.1646259438166</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3711884911846909</v>
+        <v>-0.3771118802702608</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174336078469819</v>
+        <v>1.174429372217989</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3160836986873095</v>
+        <v>-0.3211022213775696</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395578851525748</v>
+        <v>0.7395030791440735</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73207832820941</v>
+        <v>1.732122917992103</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.244112922393493</v>
+        <v>7.248433043809539</v>
       </c>
       <c r="E9" t="n">
-        <v>200.1970685028725</v>
+        <v>198.3796763826987</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3961913351432904</v>
+        <v>0.3987923271805767</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4825776086769263</v>
+        <v>0.482541079209943</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8209898843618554</v>
+        <v>0.8264422333400363</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788211039878086</v>
+        <v>0.6787777163124006</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6533192503004595</v>
+        <v>0.6532413753823039</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.723863043486536</v>
+        <v>6.683231540802822</v>
       </c>
       <c r="E10" t="n">
-        <v>219.4122266965932</v>
+        <v>218.5551811700039</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.263441070105524</v>
+        <v>-0.2730509345380813</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9629304493303683</v>
+        <v>0.9631139427959956</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2735826562434739</v>
+        <v>-0.2835084431914597</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7139965454438042</v>
+        <v>0.7138686241205822</v>
       </c>
       <c r="N10" t="n">
-        <v>1.37117846169274</v>
+        <v>1.371222028098748</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.56752194446718</v>
+        <v>6.56565741439311</v>
       </c>
       <c r="E11" t="n">
-        <v>406.1817332242671</v>
+        <v>400.3970846428522</v>
       </c>
       <c r="F11" t="n">
-        <v>0.948481588480597</v>
+        <v>0.9452125785229362</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258991828257187</v>
+        <v>0.8258953197957422</v>
       </c>
       <c r="H11" t="n">
-        <v>1.148422965180177</v>
+        <v>1.144470196000993</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6642717751585044</v>
+        <v>0.6643080515331984</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094147288431334</v>
+        <v>1.094224257383336</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.280022871703308</v>
+        <v>6.224504126018407</v>
       </c>
       <c r="E12" t="n">
-        <v>114.3697193128175</v>
+        <v>113.301260764705</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.281681978832405</v>
+        <v>-0.2901711681548071</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6618963391775272</v>
+        <v>0.6620077535210195</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4255681171804382</v>
+        <v>-0.4383198937043777</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,45 +1084,45 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7891235997329152</v>
+        <v>0.7890416641972308</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041688724045558</v>
+        <v>1.041777153701183</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.59479749581159</v>
+        <v>4.573190062438815</v>
       </c>
       <c r="E13" t="n">
-        <v>107.1853072573742</v>
+        <v>207.5977295136554</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3992914840863946</v>
+        <v>1.671834928705898</v>
       </c>
       <c r="G13" t="n">
-        <v>0.854877031193215</v>
+        <v>0.8654279715367917</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4670747598974252</v>
+        <v>1.931801355735153</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4691011235955056</v>
+        <v>0.3000688231245698</v>
       </c>
       <c r="J13" t="n">
         <v>267</v>
@@ -1138,45 +1138,45 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7601450470984181</v>
+        <v>0.603999518827068</v>
       </c>
       <c r="N13" t="n">
-        <v>1.295994239074153</v>
+        <v>1.042507858901088</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.560453588871018</v>
+        <v>4.560959182876633</v>
       </c>
       <c r="E14" t="n">
-        <v>208.3337803404335</v>
+        <v>105.627032359886</v>
       </c>
       <c r="F14" t="n">
-        <v>1.647103013950717</v>
+        <v>-0.4060831788311279</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8656070694418921</v>
+        <v>0.8547550557685566</v>
       </c>
       <c r="H14" t="n">
-        <v>1.902829900653078</v>
+        <v>-0.4750871914597761</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3000688231245698</v>
+        <v>0.4691011235955056</v>
       </c>
       <c r="J14" t="n">
         <v>267</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6039993927251441</v>
+        <v>0.7603774239430882</v>
       </c>
       <c r="N14" t="n">
-        <v>1.0427021017476</v>
+        <v>1.296231912044459</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.025864457416471</v>
+        <v>4.00588205186981</v>
       </c>
       <c r="E15" t="n">
-        <v>221.2912450709976</v>
+        <v>222.4967864150388</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06432715874131778</v>
+        <v>-0.07115691433488824</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7949968467711925</v>
+        <v>0.7951472935262961</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08091498601859452</v>
+        <v>-0.08948897256421968</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7176755692551174</v>
+        <v>0.717497539154181</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137880148693857</v>
+        <v>1.137836386788222</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.887531383330199</v>
+        <v>3.894896284852553</v>
       </c>
       <c r="E16" t="n">
-        <v>158.1762876546292</v>
+        <v>154.8180871946843</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4086073742419891</v>
+        <v>0.407260956654893</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9623666322372078</v>
+        <v>0.9623861599634363</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4245859743620808</v>
+        <v>0.4231783182234936</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158863470569953</v>
+        <v>0.5157942466666661</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9901421374766841</v>
+        <v>0.9900056641785486</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.318919089301618</v>
+        <v>3.301114578963361</v>
       </c>
       <c r="E17" t="n">
-        <v>80.2301523410262</v>
+        <v>78.75219819319032</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2301446071660826</v>
+        <v>-0.2367284032949338</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573691366977897</v>
+        <v>0.7574662054064607</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3038737598544584</v>
+        <v>-0.3125266864782489</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244775378244785</v>
+        <v>0.7243960878113884</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094297685106893</v>
+        <v>1.094337230417407</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.111085698748347</v>
+        <v>3.114521666559056</v>
       </c>
       <c r="E18" t="n">
-        <v>57.1299015904814</v>
+        <v>56.6672561501754</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4710064563236585</v>
+        <v>-0.4705235958188421</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498560822919939</v>
+        <v>0.7498552383393583</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6281291403064843</v>
+        <v>-0.6274859089614034</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645580188263136</v>
+        <v>0.7645648420311331</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143381914418989</v>
+        <v>1.143414170319022</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.958998611642519</v>
+        <v>2.960067088962361</v>
       </c>
       <c r="E19" t="n">
-        <v>102.4018192537818</v>
+        <v>98.63350981568581</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1121836350747856</v>
+        <v>0.1112434815374956</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837434829730636</v>
+        <v>0.4837386277049979</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2319072794227851</v>
+        <v>0.2299660915343236</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7178566191230589</v>
+        <v>0.7179127338451831</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6925574233682618</v>
+        <v>0.6926187461963178</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.560974912442791</v>
+        <v>2.558809510239705</v>
       </c>
       <c r="E20" t="n">
-        <v>111.207282846813</v>
+        <v>109.5691543040149</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3331319618442953</v>
+        <v>-0.3341429995089016</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825607419362621</v>
+        <v>0.7825686562674999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4256947020112953</v>
+        <v>-0.4269823444023598</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328523390500219</v>
+        <v>0.7328440831628037</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143766804413342</v>
+        <v>1.143788833064026</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.6965360570954</v>
+        <v>569.1468669228465</v>
       </c>
       <c r="E2" t="n">
-        <v>11718.87310763433</v>
+        <v>11973.27665817721</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6217366712448582</v>
+        <v>0.6295088807807374</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014044488246898</v>
+        <v>0.5014078912283693</v>
       </c>
       <c r="H2" t="n">
-        <v>1.239990336548133</v>
+        <v>1.25548259569378</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.001139616082</v>
+        <v>224.08709997092</v>
       </c>
       <c r="E3" t="n">
-        <v>4750.968996902497</v>
+        <v>4854.496724037645</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2552251479168652</v>
+        <v>0.2629094021684726</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010603236369989</v>
+        <v>0.6011109122183986</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4246248469246899</v>
+        <v>0.4373725327963287</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,45 +598,45 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907074367133997</v>
+        <v>0.8907124141948132</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067738631820603</v>
+        <v>1.067827134728993</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.52548218534151</v>
+        <v>36.95497267545513</v>
       </c>
       <c r="E4" t="n">
-        <v>381.8933319397865</v>
+        <v>1863.528761848979</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3513588954402831</v>
+        <v>0.7648436042132845</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5644793920135099</v>
+        <v>1.114678095342689</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6224476932399223</v>
+        <v>0.6861564853646347</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3496897913141569</v>
+        <v>0.3422195892575038</v>
       </c>
       <c r="J4" t="n">
         <v>267</v>
@@ -652,45 +652,45 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7366610984268909</v>
+        <v>0.4735555194548854</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8293305133904102</v>
+        <v>1.05275958695387</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.35811221292375</v>
+        <v>36.53133719023853</v>
       </c>
       <c r="E5" t="n">
-        <v>1765.407456155405</v>
+        <v>390.8710274134295</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7255069992545464</v>
+        <v>-0.349489822870822</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1148678492797</v>
+        <v>0.5644547197969308</v>
       </c>
       <c r="H5" t="n">
-        <v>0.650756051242563</v>
+        <v>-0.6191636115587004</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3422195892575038</v>
+        <v>0.3496897913141569</v>
       </c>
       <c r="J5" t="n">
         <v>267</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4735447030191164</v>
+        <v>0.7366094867680643</v>
       </c>
       <c r="N5" t="n">
-        <v>1.052921979113321</v>
+        <v>0.8292304702960047</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.8289155861603</v>
+        <v>10.7594603291563</v>
       </c>
       <c r="E6" t="n">
-        <v>1153.423085865178</v>
+        <v>1154.03304542297</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4935885254114493</v>
+        <v>-0.4943962579591383</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8092782018439753</v>
+        <v>0.8091976606017409</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6099120479048942</v>
+        <v>-0.6109709432322038</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.675957480099592</v>
+        <v>0.676482776753445</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091010770447407</v>
+        <v>1.091742451530219</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.61576852379737</v>
+        <v>10.69509587598356</v>
       </c>
       <c r="E7" t="n">
-        <v>197.716454593334</v>
+        <v>202.4492546021328</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3276570035188717</v>
+        <v>-0.3179409860338616</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182595442977088</v>
+        <v>0.7182408801108557</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4561818998719248</v>
+        <v>-0.4426662347383923</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511465068251849</v>
+        <v>0.7511627574871212</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076013882520833</v>
+        <v>1.076001813059463</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.291406613573454</v>
+        <v>9.423884146881027</v>
       </c>
       <c r="E8" t="n">
-        <v>396.1646259438166</v>
+        <v>411.0573718206031</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3771118802702608</v>
+        <v>-0.3641349641282734</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174429372217989</v>
+        <v>1.174295186368927</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3211022213775696</v>
+        <v>-0.3100881008072817</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395030791440735</v>
+        <v>0.7395324044997127</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732122917992103</v>
+        <v>1.731981801563467</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.248433043809539</v>
+        <v>7.336931234000541</v>
       </c>
       <c r="E9" t="n">
-        <v>198.3796763826987</v>
+        <v>204.2268834105678</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3987923271805767</v>
+        <v>0.428202207769973</v>
       </c>
       <c r="G9" t="n">
-        <v>0.482541079209943</v>
+        <v>0.4824815470496566</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8264422333400363</v>
+        <v>0.8874996575276335</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6787777163124006</v>
+        <v>0.6788604479734546</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532413753823039</v>
+        <v>0.6532359081278925</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.683231540802822</v>
+        <v>6.697032267331409</v>
       </c>
       <c r="E10" t="n">
-        <v>218.5551811700039</v>
+        <v>222.757661594602</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2730509345380813</v>
+        <v>-0.266369397097252</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9631139427959956</v>
+        <v>0.9629729838463146</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2835084431914597</v>
+        <v>-0.276611495405943</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7138686241205822</v>
+        <v>0.7138255077806818</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371222028098748</v>
+        <v>1.370929120180311</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.56565741439311</v>
+        <v>6.587989029124707</v>
       </c>
       <c r="E11" t="n">
-        <v>400.3970846428522</v>
+        <v>401.3416668765068</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9452125785229362</v>
+        <v>0.9541315295343467</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258953197957422</v>
+        <v>0.8259117107189691</v>
       </c>
       <c r="H11" t="n">
-        <v>1.144470196000993</v>
+        <v>1.155246398799407</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643080515331984</v>
+        <v>0.6643283496912499</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094224257383336</v>
+        <v>1.094271895937735</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.224504126018407</v>
+        <v>6.222717677607539</v>
       </c>
       <c r="E12" t="n">
-        <v>113.301260764705</v>
+        <v>113.041856669571</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2901711681548071</v>
+        <v>-0.2899828141522434</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6620077535210195</v>
+        <v>0.6620036264807955</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4383198937043777</v>
+        <v>-0.4380381051593162</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890416641972308</v>
+        <v>0.7888911943471434</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041777153701183</v>
+        <v>1.041564843100392</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.573190062438815</v>
+        <v>4.633512599202271</v>
       </c>
       <c r="E13" t="n">
-        <v>207.5977295136554</v>
+        <v>216.3124052693013</v>
       </c>
       <c r="F13" t="n">
-        <v>1.671834928705898</v>
+        <v>1.701284090244695</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8654279715367917</v>
+        <v>0.8653064086173189</v>
       </c>
       <c r="H13" t="n">
-        <v>1.931801355735153</v>
+        <v>1.966105963508571</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.603999518827068</v>
+        <v>0.6039826554703034</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042507858901088</v>
+        <v>1.042325164033217</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.560959182876633</v>
+        <v>4.558021811093807</v>
       </c>
       <c r="E14" t="n">
-        <v>105.627032359886</v>
+        <v>106.4150974073264</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4060831788311279</v>
+        <v>-0.4048498683293701</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8547550557685566</v>
+        <v>0.854768974461261</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4750871914597761</v>
+        <v>-0.4736365970518953</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7603774239430882</v>
+        <v>0.7604253436761279</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296231912044459</v>
+        <v>1.296325810860354</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.00588205186981</v>
+        <v>4.032140344507821</v>
       </c>
       <c r="E15" t="n">
-        <v>222.4967864150388</v>
+        <v>224.9997250441327</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07115691433488824</v>
+        <v>-0.06381438586110877</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7951472935262961</v>
+        <v>0.7949874630441516</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08948897256421968</v>
+        <v>-0.08027093360284183</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.717497539154181</v>
+        <v>0.7174467671808861</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137836386788222</v>
+        <v>1.13751936355263</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.894896284852553</v>
+        <v>3.973444480251892</v>
       </c>
       <c r="E16" t="n">
-        <v>154.8180871946843</v>
+        <v>163.8759844739477</v>
       </c>
       <c r="F16" t="n">
-        <v>0.407260956654893</v>
+        <v>0.4532321473838179</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9623861599634363</v>
+        <v>0.9620929300373934</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4231783182234936</v>
+        <v>0.4710897806578854</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5157942466666661</v>
+        <v>0.5158839712032719</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9900056641785486</v>
+        <v>0.9898693859770671</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.301114578963361</v>
+        <v>3.321804403623869</v>
       </c>
       <c r="E17" t="n">
-        <v>78.75219819319032</v>
+        <v>65.86885518022095</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2367284032949338</v>
+        <v>-0.2273968833029404</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7574662054064607</v>
+        <v>0.7573490711362659</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3125266864782489</v>
+        <v>-0.3002537297124724</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7243960878113884</v>
+        <v>0.7244218025479338</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094337230417407</v>
+        <v>1.094199331259937</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.114521666559056</v>
+        <v>3.128016569517881</v>
       </c>
       <c r="E18" t="n">
-        <v>56.6672561501754</v>
+        <v>56.96684773578748</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4705235958188421</v>
+        <v>-0.4672208865436331</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498552383393583</v>
+        <v>0.7498708359279448</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6274859089614034</v>
+        <v>-0.6230684861419633</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645648420311331</v>
+        <v>0.7645735976227964</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143414170319022</v>
+        <v>1.143443198257754</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.960067088962361</v>
+        <v>2.979249928075489</v>
       </c>
       <c r="E19" t="n">
-        <v>98.63350981568581</v>
+        <v>99.22824078633681</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1112434815374956</v>
+        <v>0.1244250227636954</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837386277049979</v>
+        <v>0.4839043040766324</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2299660915343236</v>
+        <v>0.2571273322338358</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7179127338451831</v>
+        <v>0.7178128792104762</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926187461963178</v>
+        <v>0.6927548366273828</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.558809510239705</v>
+        <v>2.568622274365321</v>
       </c>
       <c r="E20" t="n">
-        <v>109.5691543040149</v>
+        <v>109.909543834328</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3341429995089016</v>
+        <v>-0.3300963796684951</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825686562674999</v>
+        <v>0.7825496207172581</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4269823444023598</v>
+        <v>-0.4218216595210156</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328440831628037</v>
+        <v>0.7328323238902559</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143788833064026</v>
+        <v>1.143734805817949</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>569.1468669228465</v>
+        <v>569.3090972504385</v>
       </c>
       <c r="E2" t="n">
-        <v>11973.27665817721</v>
+        <v>11785.17040229089</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6295088807807374</v>
+        <v>0.6282730219199819</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014078912283693</v>
+        <v>0.5014051368711627</v>
       </c>
       <c r="H2" t="n">
-        <v>1.25548259569378</v>
+        <v>1.253024701423069</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.08709997092</v>
+        <v>224.1271361841924</v>
       </c>
       <c r="E3" t="n">
-        <v>4854.496724037645</v>
+        <v>4788.407056701162</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2629094021684726</v>
+        <v>0.2612808800167836</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6011109122183986</v>
+        <v>0.6010964205759071</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4373725327963287</v>
+        <v>0.4346738244863476</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907124141948132</v>
+        <v>0.8907140335913005</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067827134728993</v>
+        <v>1.067809198544434</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.95497267545513</v>
+        <v>37.10434186645239</v>
       </c>
       <c r="E4" t="n">
-        <v>1863.528761848979</v>
+        <v>1906.230205608375</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7648436042132845</v>
+        <v>0.769305296151725</v>
       </c>
       <c r="G4" t="n">
-        <v>1.114678095342689</v>
+        <v>1.114677058906644</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6861564853646347</v>
+        <v>0.690159800100592</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735555194548854</v>
+        <v>0.4735673977071961</v>
       </c>
       <c r="N4" t="n">
-        <v>1.05275958695387</v>
+        <v>1.052790797805426</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.53133719023853</v>
+        <v>36.59801336019108</v>
       </c>
       <c r="E5" t="n">
-        <v>390.8710274134295</v>
+        <v>391.2295165078735</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.349489822870822</v>
+        <v>-0.3491158351352248</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5644547197969308</v>
+        <v>0.5644510408331445</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6191636115587004</v>
+        <v>-0.6185050781728044</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366094867680643</v>
+        <v>0.7366317644543329</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292304702960047</v>
+        <v>0.8292546996060047</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.7594603291563</v>
+        <v>10.8137744125716</v>
       </c>
       <c r="E6" t="n">
-        <v>1154.03304542297</v>
+        <v>1128.83118566043</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4943962579591383</v>
+        <v>-0.4941270522434335</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8091976606017409</v>
+        <v>0.809224236204607</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6109709432322038</v>
+        <v>-0.6106182070880248</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.676482776753445</v>
+        <v>0.6763937360530559</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091742451530219</v>
+        <v>1.091640599948138</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.69509587598356</v>
+        <v>10.71900681454406</v>
       </c>
       <c r="E7" t="n">
-        <v>202.4492546021328</v>
+        <v>203.6955563834219</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3179409860338616</v>
+        <v>-0.3200695610665528</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182408801108557</v>
+        <v>0.7182273400007284</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4426662347383923</v>
+        <v>-0.4456382307393481</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511627574871212</v>
+        <v>0.7511586977862074</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076001813059463</v>
+        <v>1.075981623953775</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.423884146881027</v>
+        <v>9.476029663863184</v>
       </c>
       <c r="E8" t="n">
-        <v>411.0573718206031</v>
+        <v>412.4645896995659</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3641349641282734</v>
+        <v>-0.3626473225038183</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174295186368927</v>
+        <v>1.174296247976263</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3100881008072817</v>
+        <v>-0.3088209837413606</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395324044997127</v>
+        <v>0.7395423175956241</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731981801563467</v>
+        <v>1.732016098182414</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.336931234000541</v>
+        <v>7.315316739335712</v>
       </c>
       <c r="E9" t="n">
-        <v>204.2268834105678</v>
+        <v>210.8333610277641</v>
       </c>
       <c r="F9" t="n">
-        <v>0.428202207769973</v>
+        <v>0.4144255235148269</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824815470496566</v>
+        <v>0.4824288258305878</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8874996575276335</v>
+        <v>0.8590397201106691</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788604479734546</v>
+        <v>0.6788571678553924</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532359081278925</v>
+        <v>0.6531649604525435</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.697032267331409</v>
+        <v>6.726028599832759</v>
       </c>
       <c r="E10" t="n">
-        <v>222.757661594602</v>
+        <v>226.5527957348059</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.266369397097252</v>
+        <v>-0.264696450887812</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9629729838463146</v>
+        <v>0.9629472519821837</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.276611495405943</v>
+        <v>-0.2748815683755743</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7138255077806818</v>
+        <v>0.7138743097641365</v>
       </c>
       <c r="N10" t="n">
-        <v>1.370929120180311</v>
+        <v>1.370993741982121</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.587989029124707</v>
+        <v>6.599052974828195</v>
       </c>
       <c r="E11" t="n">
-        <v>401.3416668765068</v>
+        <v>397.0156315921157</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9541315295343467</v>
+        <v>0.95472651561247</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8259117107189691</v>
+        <v>0.8259134608838878</v>
       </c>
       <c r="H11" t="n">
-        <v>1.155246398799407</v>
+        <v>1.15596434836009</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643283496912499</v>
+        <v>0.6643232700453441</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094271895937735</v>
+        <v>1.094271858746104</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.222717677607539</v>
+        <v>6.250169633585239</v>
       </c>
       <c r="E12" t="n">
-        <v>113.041856669571</v>
+        <v>111.1251526802753</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2899828141522434</v>
+        <v>-0.2875329918004785</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6620036264807955</v>
+        <v>0.6619568038086296</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4380381051593162</v>
+        <v>-0.4343682097474199</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7888911943471434</v>
+        <v>0.7889908151697805</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041564843100392</v>
+        <v>1.041628415502958</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.633512599202271</v>
+        <v>4.634358477735186</v>
       </c>
       <c r="E13" t="n">
-        <v>216.3124052693013</v>
+        <v>218.45170126218</v>
       </c>
       <c r="F13" t="n">
-        <v>1.701284090244695</v>
+        <v>1.712155597732111</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8653064086173189</v>
+        <v>0.8652865677366557</v>
       </c>
       <c r="H13" t="n">
-        <v>1.966105963508571</v>
+        <v>1.978715100374925</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6039826554703034</v>
+        <v>0.6040241101523565</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042325164033217</v>
+        <v>1.042378529197672</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.558021811093807</v>
+        <v>4.608505176586043</v>
       </c>
       <c r="E14" t="n">
-        <v>106.4150974073264</v>
+        <v>128.2403572597396</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4048498683293701</v>
+        <v>-0.3974356100409104</v>
       </c>
       <c r="G14" t="n">
-        <v>0.854768974461261</v>
+        <v>0.8549295641088036</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4736365970518953</v>
+        <v>-0.4648752677715685</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7604253436761279</v>
+        <v>0.7603201437915077</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296325810860354</v>
+        <v>1.296397107478858</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.032140344507821</v>
+        <v>4.056170937256853</v>
       </c>
       <c r="E15" t="n">
-        <v>224.9997250441327</v>
+        <v>170.7588898676686</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06381438586110877</v>
+        <v>0.4886526321515114</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7949874630441516</v>
+        <v>0.9623842564787797</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08027093360284183</v>
+        <v>0.5077521051096767</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J15" t="n">
         <v>267</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7174467671808861</v>
+        <v>0.5158042827614021</v>
       </c>
       <c r="N15" t="n">
-        <v>1.13751936355263</v>
+        <v>0.9900216105712809</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.973444480251892</v>
+        <v>4.034995072479278</v>
       </c>
       <c r="E16" t="n">
-        <v>163.8759844739477</v>
+        <v>224.8547360124775</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4532321473838179</v>
+        <v>-0.06415624282907051</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9620929300373934</v>
+        <v>0.7949936894030105</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4710897806578854</v>
+        <v>-0.08070031710219958</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J16" t="n">
         <v>267</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158839712032719</v>
+        <v>0.7174696821509684</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9898693859770671</v>
+        <v>1.137570853795551</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.321804403623869</v>
+        <v>3.331113441390348</v>
       </c>
       <c r="E17" t="n">
-        <v>65.86885518022095</v>
+        <v>64.45860947209408</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2273968833029404</v>
+        <v>-0.2266637132140285</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573490711362659</v>
+        <v>0.7573457452325086</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3002537297124724</v>
+        <v>-0.299286969842871</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244218025479338</v>
+        <v>0.7244388206848364</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094199331259937</v>
+        <v>1.094226241778401</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.128016569517881</v>
+        <v>3.132114147673872</v>
       </c>
       <c r="E18" t="n">
-        <v>56.96684773578748</v>
+        <v>56.99469197821863</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4672208865436331</v>
+        <v>-0.4671402638080695</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498708359279448</v>
+        <v>0.7498716819993156</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6230684861419633</v>
+        <v>-0.6229602677655133</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645735976227964</v>
+        <v>0.7645692043914474</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143443198257754</v>
+        <v>1.143444199394414</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.979249928075489</v>
+        <v>2.984514443957418</v>
       </c>
       <c r="E19" t="n">
-        <v>99.22824078633681</v>
+        <v>98.69449944819374</v>
       </c>
       <c r="F19" t="n">
         <v>0.1244250227636954</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7178128792104762</v>
+        <v>0.7177822009764523</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6927548366273828</v>
+        <v>0.692729034667535</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.568622274365321</v>
+        <v>2.571171381928921</v>
       </c>
       <c r="E20" t="n">
-        <v>109.909543834328</v>
+        <v>109.8405176562848</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3300963796684951</v>
+        <v>-0.3306025670272275</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825496207172581</v>
+        <v>0.7825501594591221</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4218216595210156</v>
+        <v>-0.422468212460312</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328323238902559</v>
+        <v>0.7328334366914434</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143734805817949</v>
+        <v>1.143743612836623</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.4946310453963</v>
+        <v>568.8659070340146</v>
       </c>
       <c r="E2" t="n">
-        <v>10502.26852507295</v>
+        <v>10380.35028771494</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6250586873821851</v>
+        <v>0.6281962168490942</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014018790123776</v>
+        <v>0.5014049932107104</v>
       </c>
       <c r="H2" t="n">
-        <v>1.24662214791332</v>
+        <v>1.25287188072557</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.6942802764489</v>
+        <v>223.7171315287128</v>
       </c>
       <c r="E3" t="n">
-        <v>4230.555876317903</v>
+        <v>4167.982922440735</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2571935578168492</v>
+        <v>0.2588576482146621</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010689769912243</v>
+        <v>0.6010786077958561</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4278935823710034</v>
+        <v>0.430655233537404</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907183548353665</v>
+        <v>0.8907300385221554</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067772564759343</v>
+        <v>1.067797047748686</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.0140392808348</v>
+        <v>36.96551801757813</v>
       </c>
       <c r="E4" t="n">
-        <v>1797.966246959096</v>
+        <v>1779.0342166068</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7596992590186749</v>
+        <v>0.7665592816092779</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11468444424714</v>
+        <v>1.114677205948</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6815375086101404</v>
+        <v>0.6876962025587862</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.473564645803331</v>
+        <v>0.4735632376323339</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052798495813672</v>
+        <v>1.052781990030695</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.55580685244608</v>
+        <v>36.58990531566115</v>
       </c>
       <c r="E5" t="n">
-        <v>366.7333002585482</v>
+        <v>372.3210384223963</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3506114396957315</v>
+        <v>-0.3479935257615676</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5644682676884569</v>
+        <v>0.5644425150565161</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6211357834719631</v>
+        <v>-0.6165260703771117</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366371361174884</v>
+        <v>0.7366528037328278</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292914437382074</v>
+        <v>0.8292660960551232</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.87073611303743</v>
+        <v>11.26760169386142</v>
       </c>
       <c r="E6" t="n">
-        <v>1036.702409036859</v>
+        <v>1227.81620512309</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4879247221744244</v>
+        <v>-0.4641904952117711</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8099103479059739</v>
+        <v>0.8138161920918856</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6024428795556884</v>
+        <v>-0.5703873917998437</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6756377884527959</v>
+        <v>0.6727977739232333</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091352185161473</v>
+        <v>1.091998942643173</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.67960855649476</v>
+        <v>10.66409521157467</v>
       </c>
       <c r="E7" t="n">
-        <v>182.242699230469</v>
+        <v>181.4907918277047</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3237143863800342</v>
+        <v>-0.3228036732820584</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182270886226552</v>
+        <v>0.7182244324597012</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4507131400471426</v>
+        <v>-0.4494468006004106</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511513531258253</v>
+        <v>0.751144852249037</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075977717780374</v>
+        <v>1.075957743753212</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.418079662966836</v>
+        <v>9.403967539540904</v>
       </c>
       <c r="E8" t="n">
-        <v>361.6960134212046</v>
+        <v>361.0250940717754</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3682211602139412</v>
+        <v>-0.3659932027673439</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174309610907469</v>
+        <v>1.174298589549306</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3135639500807557</v>
+        <v>-0.3116696264685216</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395324361920291</v>
+        <v>0.7395274869205872</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732023918834727</v>
+        <v>1.731985314431922</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.336713215824555</v>
+        <v>7.337040096582997</v>
       </c>
       <c r="E9" t="n">
-        <v>210.6231367813968</v>
+        <v>212.6606471044763</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4210718600951961</v>
+        <v>0.4220220193415301</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824365978462097</v>
+        <v>0.4824404023045959</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8728024821811398</v>
+        <v>0.874765084610555</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788601198744176</v>
+        <v>0.6788746527085535</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531825674263168</v>
+        <v>0.6531976446223221</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.692819796218812</v>
+        <v>6.664545415606041</v>
       </c>
       <c r="E10" t="n">
-        <v>217.3870792675931</v>
+        <v>221.913137734986</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2691553654537989</v>
+        <v>-0.2699906007311133</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9630243223861695</v>
+        <v>0.9630417839419625</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2794896859789472</v>
+        <v>-0.2803519070854605</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7138622271295997</v>
+        <v>0.7137831973583563</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371089172846107</v>
+        <v>1.370953726108816</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.553019827076652</v>
+        <v>6.55181541505561</v>
       </c>
       <c r="E11" t="n">
-        <v>357.6247401642199</v>
+        <v>360.8074106338696</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9339309862902332</v>
+        <v>0.9392727021364888</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8259011027797678</v>
+        <v>0.8258946652556656</v>
       </c>
       <c r="H11" t="n">
-        <v>1.130802444925748</v>
+        <v>1.137279052221176</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.664311602536466</v>
+        <v>0.664309043886787</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094243376600345</v>
+        <v>1.094223836731169</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.251515298561502</v>
+        <v>6.261441176838637</v>
       </c>
       <c r="E12" t="n">
-        <v>101.005760804879</v>
+        <v>97.9793824450132</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2877215200914802</v>
+        <v>-0.2833819832896969</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6619599552665673</v>
+        <v>0.6619064617724983</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4346509449738791</v>
+        <v>-0.4281299543908927</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890389773209172</v>
+        <v>0.7890783519563194</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041703727077653</v>
+        <v>1.041665055348166</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.623759239945996</v>
+        <v>4.630694273098436</v>
       </c>
       <c r="E13" t="n">
-        <v>126.7030865158827</v>
+        <v>127.3690625991577</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.394339074416225</v>
+        <v>-0.3912382822822094</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8550354618088962</v>
+        <v>0.8551642805179066</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4611961632351119</v>
+        <v>-0.4575007296203564</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7601607011583568</v>
+        <v>0.7601465694523747</v>
       </c>
       <c r="N13" t="n">
-        <v>1.296294217014422</v>
+        <v>1.296457360728193</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.608240024337819</v>
+        <v>4.589892889494509</v>
       </c>
       <c r="E14" t="n">
-        <v>209.0277641206035</v>
+        <v>211.2641674599272</v>
       </c>
       <c r="F14" t="n">
-        <v>1.671834928705898</v>
+        <v>1.678027545886724</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8654279715367917</v>
+        <v>0.865394156745828</v>
       </c>
       <c r="H14" t="n">
-        <v>1.931801355735153</v>
+        <v>1.939032674078446</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6039384793862868</v>
+        <v>0.6039057396406194</v>
       </c>
       <c r="N14" t="n">
-        <v>1.042407846930678</v>
+        <v>1.042304136150944</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.014429662137772</v>
+        <v>3.996708179340737</v>
       </c>
       <c r="E15" t="n">
-        <v>171.8791983174474</v>
+        <v>213.2532733602604</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4654671531493455</v>
+        <v>-0.06706067288906503</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9621432154366314</v>
+        <v>0.7950513707968172</v>
       </c>
       <c r="H15" t="n">
-        <v>0.483781567734811</v>
+        <v>-0.08434759734060381</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J15" t="n">
         <v>267</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5158499023246437</v>
+        <v>0.7174079144666685</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9898676181328246</v>
+        <v>1.137555775352074</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.011555371074091</v>
+        <v>3.961844708199985</v>
       </c>
       <c r="E16" t="n">
-        <v>205.3949379208381</v>
+        <v>174.2208483427864</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.07081574577769589</v>
+        <v>0.4464468388029856</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7951386521534896</v>
+        <v>0.9620881306264699</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.08906087710099896</v>
+        <v>0.4640394414930354</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J16" t="n">
         <v>267</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7174104899822722</v>
+        <v>0.5158703915890742</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137691807555425</v>
+        <v>0.9898441128624877</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.33475708354987</v>
+        <v>3.325854690984842</v>
       </c>
       <c r="E17" t="n">
-        <v>59.29824220260168</v>
+        <v>58.5705905800106</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2250133981102547</v>
+        <v>-0.2257469881015298</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573413793538317</v>
+        <v>0.7573427868509025</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2971096050531895</v>
+        <v>-0.2980776895495441</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244604297492467</v>
+        <v>0.7244468344308446</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09425968293992</v>
+        <v>1.094234385261903</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.121277918482836</v>
+        <v>3.111259748590274</v>
       </c>
       <c r="E18" t="n">
-        <v>53.44382684272097</v>
+        <v>53.36849358585087</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4697990833404916</v>
+        <v>-0.4711673835367207</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498554691626944</v>
+        <v>0.7498565410019934</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.62651951297372</v>
+        <v>-0.6283433667286876</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645669296867655</v>
+        <v>0.7645539436425828</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143423504706087</v>
+        <v>1.143398616591626</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.965207189245291</v>
+        <v>2.965529700648279</v>
       </c>
       <c r="E19" t="n">
-        <v>95.29742788215313</v>
+        <v>92.99683017919642</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1112434815374956</v>
+        <v>0.1178290353823448</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837386277049979</v>
+        <v>0.4837951646748244</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2299660915343236</v>
+        <v>0.2435514944874279</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7179372040945603</v>
+        <v>0.7179053242930068</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926459042617439</v>
+        <v>0.6926917946373764</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.563028704999231</v>
+        <v>2.564838615631475</v>
       </c>
       <c r="E20" t="n">
-        <v>103.6146085161548</v>
+        <v>103.3787423545446</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3341429995089016</v>
+        <v>-0.3321205124569014</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825686562674999</v>
+        <v>0.7825549312057299</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4269823444023598</v>
+        <v>-0.4244053665921997</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732823589064458</v>
+        <v>0.7328205870991973</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143762708877168</v>
+        <v>1.143730860060579</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.8659070340146</v>
+        <v>568.9489272002664</v>
       </c>
       <c r="E2" t="n">
-        <v>10380.35028771494</v>
+        <v>10333.24601287458</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6281962168490942</v>
+        <v>0.6291225052387526</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014049932107104</v>
+        <v>0.5014069405521683</v>
       </c>
       <c r="H2" t="n">
-        <v>1.25287188072557</v>
+        <v>1.254714393354705</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.7171315287128</v>
+        <v>223.8390379889875</v>
       </c>
       <c r="E3" t="n">
-        <v>4167.982922440735</v>
+        <v>4173.405946795026</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2588576482146621</v>
+        <v>0.2602078444133507</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010786077958561</v>
+        <v>0.6010879790699672</v>
       </c>
       <c r="H3" t="n">
-        <v>0.430655233537404</v>
+        <v>0.4328947732675622</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907300385221554</v>
+        <v>0.8907287031427644</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067797047748686</v>
+        <v>1.06780794753676</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.96551801757813</v>
+        <v>36.97595042058004</v>
       </c>
       <c r="E4" t="n">
-        <v>1779.0342166068</v>
+        <v>1794.420861838436</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7665592816092779</v>
+        <v>0.7596992590186749</v>
       </c>
       <c r="G4" t="n">
-        <v>1.114677205948</v>
+        <v>1.11468444424714</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6876962025587862</v>
+        <v>0.6815375086101404</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735632376323339</v>
+        <v>0.473544286921823</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052781990030695</v>
+        <v>1.052742608055185</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.58990531566115</v>
+        <v>36.63642533575322</v>
       </c>
       <c r="E5" t="n">
-        <v>372.3210384223963</v>
+        <v>372.5161241271791</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3479935257615676</v>
+        <v>-0.3487417896949202</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5644425150565161</v>
+        <v>0.5644477803837999</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6165260703771117</v>
+        <v>-0.617845975862977</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366528037328278</v>
+        <v>0.7366309160870474</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292660960551232</v>
+        <v>0.8292459715247176</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.26760169386142</v>
+        <v>11.63594924611697</v>
       </c>
       <c r="E6" t="n">
-        <v>1227.81620512309</v>
+        <v>1362.713404329063</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4641904952117711</v>
+        <v>-0.437679186652263</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8138161920918856</v>
+        <v>0.8204828454221175</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5703873917998437</v>
+        <v>-0.5334409964745677</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6727977739232333</v>
+        <v>0.6676918777399988</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091998942643173</v>
+        <v>1.092585058974373</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.66409521157467</v>
+        <v>10.67080251971401</v>
       </c>
       <c r="E7" t="n">
-        <v>181.4907918277047</v>
+        <v>181.0012193070981</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3228036732820584</v>
+        <v>-0.3225000291378001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182244324597012</v>
+        <v>0.7182239498869362</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4494468006004106</v>
+        <v>-0.4490243317402162</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.751144852249037</v>
+        <v>0.7511433404048364</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075957743753212</v>
+        <v>1.075950676475925</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.403967539540904</v>
+        <v>9.445584740711832</v>
       </c>
       <c r="E8" t="n">
-        <v>361.0250940717754</v>
+        <v>358.8127399118252</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3659932027673439</v>
+        <v>-0.3641349641282734</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174298589549306</v>
+        <v>1.174295186368927</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3116696264685216</v>
+        <v>-0.3100881008072817</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395274869205872</v>
+        <v>0.7395339324999538</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731985314431922</v>
+        <v>1.73198866400778</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.337040096582997</v>
+        <v>7.33595069491033</v>
       </c>
       <c r="E9" t="n">
-        <v>212.6606471044763</v>
+        <v>211.9866281553778</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4220220193415301</v>
+        <v>0.4224971629015548</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824404023045959</v>
+        <v>0.4824425571002083</v>
       </c>
       <c r="H9" t="n">
-        <v>0.874765084610555</v>
+        <v>0.8757460482778219</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788746527085535</v>
+        <v>0.6788786661994843</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531976446223221</v>
+        <v>0.6532018869172027</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.664545415606041</v>
+        <v>6.691893920173107</v>
       </c>
       <c r="E10" t="n">
-        <v>221.913137734986</v>
+        <v>224.4306801502108</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2699906007311133</v>
+        <v>-0.2670661559591079</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9630417839419625</v>
+        <v>0.9629848280426186</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2803519070854605</v>
+        <v>-0.2773316340839467</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7137831973583563</v>
+        <v>0.7138201756010022</v>
       </c>
       <c r="N10" t="n">
-        <v>1.370953726108816</v>
+        <v>1.370938340617093</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.55181541505561</v>
+        <v>6.562395594764063</v>
       </c>
       <c r="E11" t="n">
-        <v>360.8074106338696</v>
+        <v>364.4594094910062</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9392727021364888</v>
+        <v>0.942836042712843</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258946652556656</v>
+        <v>0.8258940717851987</v>
       </c>
       <c r="H11" t="n">
-        <v>1.137279052221176</v>
+        <v>1.141594394393545</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.664309043886787</v>
+        <v>0.6643141776526704</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094223836731169</v>
+        <v>1.094227256850498</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.261441176838637</v>
+        <v>6.274723518497233</v>
       </c>
       <c r="E12" t="n">
-        <v>97.9793824450132</v>
+        <v>93.75049730608551</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2833819832896969</v>
+        <v>-0.2830042979948146</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6619064617724983</v>
+        <v>0.6619036868047524</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4281299543908927</v>
+        <v>-0.4275611446749577</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890783519563194</v>
+        <v>0.7890752839954973</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041665055348166</v>
+        <v>1.041652592738264</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.630694273098436</v>
+        <v>4.639683980339335</v>
       </c>
       <c r="E13" t="n">
-        <v>127.3690625991577</v>
+        <v>129.2136194065222</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3912382822822094</v>
+        <v>-0.3899967758597839</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8551642805179066</v>
+        <v>0.8552222236258501</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4575007296203564</v>
+        <v>-0.4560180559928982</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7601465694523747</v>
+        <v>0.760132058474183</v>
       </c>
       <c r="N13" t="n">
-        <v>1.296457360728193</v>
+        <v>1.296515418357973</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.589892889494509</v>
+        <v>4.612063771066961</v>
       </c>
       <c r="E14" t="n">
-        <v>211.2641674599272</v>
+        <v>211.5596154346895</v>
       </c>
       <c r="F14" t="n">
-        <v>1.678027545886724</v>
+        <v>1.693525911024945</v>
       </c>
       <c r="G14" t="n">
-        <v>0.865394156745828</v>
+        <v>0.8653288051121129</v>
       </c>
       <c r="H14" t="n">
-        <v>1.939032674078446</v>
+        <v>1.957089491324087</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6039057396406194</v>
+        <v>0.6039586425635476</v>
       </c>
       <c r="N14" t="n">
-        <v>1.042304136150944</v>
+        <v>1.042312677066489</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.996708179340737</v>
+        <v>4.017882146625001</v>
       </c>
       <c r="E15" t="n">
-        <v>213.2532733602604</v>
+        <v>216.8698476213139</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06706067288906503</v>
+        <v>-0.06569418422408713</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7950513707968172</v>
+        <v>0.7950231661997288</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08434759734060381</v>
+        <v>-0.08263178611273722</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7174079144666685</v>
+        <v>0.7174144992072858</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137555775352074</v>
+        <v>1.137521443179997</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.961844708199985</v>
+        <v>3.962838831835697</v>
       </c>
       <c r="E16" t="n">
-        <v>174.2208483427864</v>
+        <v>176.5590279002405</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4464468388029856</v>
+        <v>0.4396700656303327</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9620881306264699</v>
+        <v>0.9620998581174198</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4640394414930354</v>
+        <v>0.456990053496789</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158703915890742</v>
+        <v>0.5158426065902169</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9898441128624877</v>
+        <v>0.9897990204619665</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.325854690984842</v>
+        <v>3.340377805426455</v>
       </c>
       <c r="E17" t="n">
-        <v>58.5705905800106</v>
+        <v>59.23962617816719</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2257469881015298</v>
+        <v>-0.2211589929467375</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573427868509025</v>
+        <v>0.7573479785241979</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2980776895495441</v>
+        <v>-0.2920176711604853</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244468344308446</v>
+        <v>0.7244666946844109</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094234385261903</v>
+        <v>1.094267634435068</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.111259748590274</v>
+        <v>3.12194850561702</v>
       </c>
       <c r="E18" t="n">
-        <v>53.36849358585087</v>
+        <v>53.71888663372946</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4711673835367207</v>
+        <v>-0.4686715354431937</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498565410019934</v>
+        <v>0.7498593982429409</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6283433667286876</v>
+        <v>-0.6250125510747451</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645539436425828</v>
+        <v>0.7645701674599189</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143398616591626</v>
+        <v>1.143422795573267</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.965529700648279</v>
+        <v>2.971328092518307</v>
       </c>
       <c r="E19" t="n">
-        <v>92.99683017919642</v>
+        <v>90.81860755294782</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1178290353823448</v>
+        <v>0.1168876025234917</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837951646748244</v>
+        <v>0.4837838667918475</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2435514944874279</v>
+        <v>0.2416112039837486</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7179053242930068</v>
+        <v>0.7179284699933873</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926917946373764</v>
+        <v>0.6926952604821777</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.564838615631475</v>
+        <v>2.575823965518958</v>
       </c>
       <c r="E20" t="n">
-        <v>103.3787423545446</v>
+        <v>103.649520347752</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3321205124569014</v>
+        <v>-0.328070603447956</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825549312057299</v>
+        <v>0.7825527249733916</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4244053665921997</v>
+        <v>-0.4192313092502631</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328205870991973</v>
+        <v>0.7328457380545754</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143730860060579</v>
+        <v>1.143762447061851</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.9489272002664</v>
+        <v>568.7248624858699</v>
       </c>
       <c r="E2" t="n">
-        <v>10333.24601287458</v>
+        <v>10333.60925823173</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6291225052387526</v>
+        <v>0.6268283370436722</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014069405521683</v>
+        <v>0.5014029742155748</v>
       </c>
       <c r="H2" t="n">
-        <v>1.254714393354705</v>
+        <v>1.250148820964456</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.8390379889875</v>
+        <v>223.7120703878112</v>
       </c>
       <c r="E3" t="n">
-        <v>4173.405946795026</v>
+        <v>4180.119142542317</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2602078444133507</v>
+        <v>0.2573506966347479</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010879790699672</v>
+        <v>0.6010697957647153</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4328947732675622</v>
+        <v>0.4281544313956611</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907287031427644</v>
+        <v>0.8907295848913804</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06780794753676</v>
+        <v>1.067785149280076</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.97595042058004</v>
+        <v>37.0827180505095</v>
       </c>
       <c r="E4" t="n">
-        <v>1794.420861838436</v>
+        <v>1764.940322512731</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7596992590186749</v>
+        <v>0.766902470794486</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11468444424714</v>
+        <v>1.114677101683836</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6815375086101404</v>
+        <v>0.6880041490365235</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.473544286921823</v>
+        <v>0.4735665074327406</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052742608055185</v>
+        <v>1.052793399930469</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.63642533575322</v>
+        <v>36.57025346955577</v>
       </c>
       <c r="E5" t="n">
-        <v>372.5161241271791</v>
+        <v>370.8818193393795</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3487417896949202</v>
+        <v>-0.3498637528863531</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5644477803837999</v>
+        <v>0.5644588172669761</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.617845975862977</v>
+        <v>-0.6198215745487691</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366309160870474</v>
+        <v>0.7366319319028362</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292459715247176</v>
+        <v>0.8292698895403697</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.63594924611697</v>
+        <v>11.55940321701903</v>
       </c>
       <c r="E6" t="n">
-        <v>1362.713404329063</v>
+        <v>1428.464654229988</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.437679186652263</v>
+        <v>-0.4442241359018805</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8204828454221175</v>
+        <v>0.8186185600319885</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5334409964745677</v>
+        <v>-0.5426509458624074</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6676918777399988</v>
+        <v>0.668770647211492</v>
       </c>
       <c r="N6" t="n">
-        <v>1.092585058974373</v>
+        <v>1.091872390801879</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.67080251971401</v>
+        <v>10.64496340003629</v>
       </c>
       <c r="E7" t="n">
-        <v>181.0012193070981</v>
+        <v>178.5111245155196</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3225000291378001</v>
+        <v>-0.3255348248854814</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182239498869362</v>
+        <v>0.7182378388634304</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4490243317402162</v>
+        <v>-0.4532409840737732</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511433404048364</v>
+        <v>0.751126009077619</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075950676475925</v>
+        <v>1.075955168231757</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.445584740711832</v>
+        <v>9.420744772111576</v>
       </c>
       <c r="E8" t="n">
-        <v>358.8127399118252</v>
+        <v>356.5874286367179</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3641349641282734</v>
+        <v>-0.3671074447156448</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174295186368927</v>
+        <v>1.174303154209101</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3100881008072817</v>
+        <v>-0.3126172687178835</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395339324999538</v>
+        <v>0.7395283834044516</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73198866400778</v>
+        <v>1.732001120690658</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.33595069491033</v>
+        <v>7.339440431183662</v>
       </c>
       <c r="E9" t="n">
-        <v>211.9866281553778</v>
+        <v>212.0520068571872</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4224971629015548</v>
+        <v>0.4227347506628969</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824425571002083</v>
+        <v>0.4824436976386611</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8757460482778219</v>
+        <v>0.8762364452722424</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788786661994843</v>
+        <v>0.6788642419909201</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532018869172027</v>
+        <v>0.6531947195031078</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.691893920173107</v>
+        <v>6.67659610542252</v>
       </c>
       <c r="E10" t="n">
-        <v>224.4306801502108</v>
+        <v>224.6538550954835</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2670661559591079</v>
+        <v>-0.2716603016467474</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9629848280426186</v>
+        <v>0.9630795590311234</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2773316340839467</v>
+        <v>-0.2820746210417371</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7138201756010022</v>
+        <v>0.7137806513066114</v>
       </c>
       <c r="N10" t="n">
-        <v>1.370938340617093</v>
+        <v>1.371008131694417</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.562395594764063</v>
+        <v>6.553648935054658</v>
       </c>
       <c r="E11" t="n">
-        <v>364.4594094910062</v>
+        <v>363.5825739830267</v>
       </c>
       <c r="F11" t="n">
-        <v>0.942836042712843</v>
+        <v>0.9348209975044466</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258940717851987</v>
+        <v>0.8258995675867911</v>
       </c>
       <c r="H11" t="n">
-        <v>1.141594394393545</v>
+        <v>1.131882173320316</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643141776526704</v>
+        <v>0.6643046866371889</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094227256850498</v>
+        <v>1.094227560771598</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.274723518497233</v>
+        <v>6.259570455899627</v>
       </c>
       <c r="E12" t="n">
-        <v>93.75049730608551</v>
+        <v>93.55815228106286</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2830042979948146</v>
+        <v>-0.2848921899661258</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6619036868047524</v>
+        <v>0.6619205644047242</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4275611446749577</v>
+        <v>-0.4304023855526136</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890752839954973</v>
+        <v>0.7890684120069236</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041652592738264</v>
+        <v>1.041678321606849</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.639683980339335</v>
+        <v>4.63184232177503</v>
       </c>
       <c r="E13" t="n">
-        <v>129.2136194065222</v>
+        <v>130.2400617948161</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3899967758597839</v>
+        <v>-0.3930992677794305</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8552222236258501</v>
+        <v>0.8550842393102555</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4560180559928982</v>
+        <v>-0.4597199313327536</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.760132058474183</v>
+        <v>0.7601690065187585</v>
       </c>
       <c r="N13" t="n">
-        <v>1.296515418357973</v>
+        <v>1.296379499350274</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.612063771066961</v>
+        <v>4.616836460591781</v>
       </c>
       <c r="E14" t="n">
-        <v>211.5596154346895</v>
+        <v>209.6372428465778</v>
       </c>
       <c r="F14" t="n">
-        <v>1.693525911024945</v>
+        <v>1.6888738806286</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8653288051121129</v>
+        <v>0.8653455325440599</v>
       </c>
       <c r="H14" t="n">
-        <v>1.957089491324087</v>
+        <v>1.951675737740761</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6039586425635476</v>
+        <v>0.6039735809403104</v>
       </c>
       <c r="N14" t="n">
-        <v>1.042312677066489</v>
+        <v>1.042366852448362</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.017882146625001</v>
+        <v>4.013974493773963</v>
       </c>
       <c r="E15" t="n">
-        <v>216.8698476213139</v>
+        <v>215.647924632706</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06569418422408713</v>
+        <v>-0.06945073524001111</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7950231661997288</v>
+        <v>0.7951052644175722</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08263178611273722</v>
+        <v>-0.08734784983581378</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7174144992072858</v>
+        <v>0.7173904858839248</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137521443179997</v>
+        <v>1.137609829422649</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.962838831835697</v>
+        <v>3.933689011872034</v>
       </c>
       <c r="E16" t="n">
-        <v>176.5590279002405</v>
+        <v>179.2827818230267</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4396700656303327</v>
+        <v>0.428845028616444</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9620998581174198</v>
+        <v>0.9621529962315742</v>
       </c>
       <c r="H16" t="n">
-        <v>0.456990053496789</v>
+        <v>0.4457139667974678</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158426065902169</v>
+        <v>0.5158162376685548</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9897990204619665</v>
+        <v>0.989810918760764</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.340377805426455</v>
+        <v>3.335905840042511</v>
       </c>
       <c r="E17" t="n">
-        <v>59.23962617816719</v>
+        <v>59.39668048613846</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2211589929467375</v>
+        <v>-0.2246465331756468</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573479785241979</v>
+        <v>0.7573409953431874</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2920176711604853</v>
+        <v>-0.296625343876768</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244666946844109</v>
+        <v>0.7244580757364104</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094267634435068</v>
+        <v>1.094253182325021</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.12194850561702</v>
+        <v>3.114968255887765</v>
       </c>
       <c r="E18" t="n">
-        <v>53.71888663372946</v>
+        <v>53.84917280753641</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4686715354431937</v>
+        <v>-0.4712478422131086</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498593982429409</v>
+        <v>0.7498568036179979</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6250125510747451</v>
+        <v>-0.6284504453908749</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645701674599189</v>
+        <v>0.7645591777183648</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143422795573267</v>
+        <v>1.143411448800475</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.971328092518307</v>
+        <v>2.967560056128868</v>
       </c>
       <c r="E19" t="n">
-        <v>90.81860755294782</v>
+        <v>88.49913021767232</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1168876025234917</v>
+        <v>0.1150053759251475</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837838667918475</v>
+        <v>0.4837644919623301</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2416112039837486</v>
+        <v>0.2377300894049552</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7179284699933873</v>
+        <v>0.7179208729771123</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926952604821777</v>
+        <v>0.6926656686236651</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.575823965518958</v>
+        <v>2.573733701399156</v>
       </c>
       <c r="E20" t="n">
-        <v>103.649520347752</v>
+        <v>103.6312354752308</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.328070603447956</v>
+        <v>-0.3295900895952948</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825527249733916</v>
+        <v>0.7825496078982574</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4192313092502631</v>
+        <v>-0.4211746913789856</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328457380545754</v>
+        <v>0.7328424516699201</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143762447061851</v>
+        <v>1.143761809755295</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.7248624858699</v>
+        <v>567.8175165076744</v>
       </c>
       <c r="E2" t="n">
-        <v>10333.60925823173</v>
+        <v>10375.17266899911</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6268283370436722</v>
+        <v>0.6250556471921012</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014029742155748</v>
+        <v>0.5014018786039043</v>
       </c>
       <c r="H2" t="n">
-        <v>1.250148820964456</v>
+        <v>1.246616085548974</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.7120703878112</v>
+        <v>223.4570890773376</v>
       </c>
       <c r="E3" t="n">
-        <v>4180.119142542317</v>
+        <v>4178.257157636012</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2573506966347479</v>
+        <v>0.2571843145211903</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010697957647153</v>
+        <v>0.6010689294179261</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4281544313956611</v>
+        <v>0.4278782381419167</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907295848913804</v>
+        <v>0.8907183993155562</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067785149280076</v>
+        <v>1.067772534439166</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.0827180505095</v>
+        <v>36.88942399702586</v>
       </c>
       <c r="E4" t="n">
-        <v>1764.940322512731</v>
+        <v>1755.215496085001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.766902470794486</v>
+        <v>0.761756513234386</v>
       </c>
       <c r="G4" t="n">
-        <v>1.114677101683836</v>
+        <v>1.11468124215865</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6880041490365235</v>
+        <v>0.6833850650964544</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735665074327406</v>
+        <v>0.4735662452418829</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052793399930469</v>
+        <v>1.052799028117801</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.57025346955577</v>
+        <v>36.50852069960956</v>
       </c>
       <c r="E5" t="n">
-        <v>370.8818193393795</v>
+        <v>370.0828981346877</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3498637528863531</v>
+        <v>-0.3509851964588095</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5644588172669761</v>
+        <v>0.5644736206188732</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6198215745487691</v>
+        <v>-0.6217920264794644</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366319319028362</v>
+        <v>0.7366299651769679</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292698895403697</v>
+        <v>0.8292912357200724</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.55940321701903</v>
+        <v>11.43455372362824</v>
       </c>
       <c r="E6" t="n">
-        <v>1428.464654229988</v>
+        <v>1459.3188580637</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4442241359018805</v>
+        <v>-0.4535906041620639</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8186185600319885</v>
+        <v>0.8161976092269488</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5426509458624074</v>
+        <v>-0.5557362568014337</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.668770647211492</v>
+        <v>0.6704515359423083</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091872390801879</v>
+        <v>1.091381911576242</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.64496340003629</v>
+        <v>10.58381478112146</v>
       </c>
       <c r="E7" t="n">
-        <v>178.5111245155196</v>
+        <v>180.3285084435689</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3255348248854814</v>
+        <v>-0.3315934229673613</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182378388634304</v>
+        <v>0.7183260325081172</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4532409840737732</v>
+        <v>-0.4616196656684779</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.751126009077619</v>
+        <v>0.7510443878477887</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075955168231757</v>
+        <v>1.075972704494747</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.420744772111576</v>
+        <v>9.369193047452695</v>
       </c>
       <c r="E8" t="n">
-        <v>356.5874286367179</v>
+        <v>357.0556344120241</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3671074447156448</v>
+        <v>-0.3711884911846909</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174303154209101</v>
+        <v>1.174336078469819</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3126172687178835</v>
+        <v>-0.3160836986873095</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395283834044516</v>
+        <v>0.7395149216046094</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732001120690658</v>
+        <v>1.732021937024131</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.339440431183662</v>
+        <v>7.306390086321613</v>
       </c>
       <c r="E9" t="n">
-        <v>212.0520068571872</v>
+        <v>213.2428486519044</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4227347506628969</v>
+        <v>0.4141883091329075</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824436976386611</v>
+        <v>0.4824291586694995</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8762364452722424</v>
+        <v>0.858547419221519</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788642419909201</v>
+        <v>0.6788683847885997</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531947195031078</v>
+        <v>0.6531804480525454</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.67659610542252</v>
+        <v>6.574915325177023</v>
       </c>
       <c r="E10" t="n">
-        <v>224.6538550954835</v>
+        <v>232.2131401931072</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2716603016467474</v>
+        <v>-0.2876093571894656</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9630795590311234</v>
+        <v>0.9636343059428863</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2820746210417371</v>
+        <v>-0.298463177800679</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7137806513066114</v>
+        <v>0.7134047932798522</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371008131694417</v>
+        <v>1.371078494445843</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.553648935054658</v>
+        <v>6.536170353845875</v>
       </c>
       <c r="E11" t="n">
-        <v>363.5825739830267</v>
+        <v>364.8608492584005</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9348209975044466</v>
+        <v>0.9291861174664535</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258995675867911</v>
+        <v>0.8259124133153521</v>
       </c>
       <c r="H11" t="n">
-        <v>1.131882173320316</v>
+        <v>1.125041956612013</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643046866371889</v>
+        <v>0.6643018753135939</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094227560771598</v>
+        <v>1.094242340171982</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.259570455899627</v>
+        <v>6.227406653420942</v>
       </c>
       <c r="E12" t="n">
-        <v>93.55815228106286</v>
+        <v>93.11765205551686</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2848921899661258</v>
+        <v>-0.290359508739045</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6619205644047242</v>
+        <v>0.6620119555969249</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4304023855526136</v>
+        <v>-0.4386016087537766</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890684120069236</v>
+        <v>0.7889758430886464</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041678321606849</v>
+        <v>1.041702201547716</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.63184232177503</v>
+        <v>4.600462475400146</v>
       </c>
       <c r="E13" t="n">
-        <v>130.2400617948161</v>
+        <v>131.7268274266928</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3930992677794305</v>
+        <v>-0.3986730302047174</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8550842393102555</v>
+        <v>0.8548936248812056</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4597199313327536</v>
+        <v>-0.4663422659867376</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7601690065187585</v>
+        <v>0.7602848878701731</v>
       </c>
       <c r="N13" t="n">
-        <v>1.296379499350274</v>
+        <v>1.29629092245023</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.616836460591781</v>
+        <v>4.583397043740528</v>
       </c>
       <c r="E14" t="n">
-        <v>209.6372428465778</v>
+        <v>206.8139969343039</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6888738806286</v>
+        <v>1.657915627499413</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8653455325440599</v>
+        <v>0.8655200847096125</v>
       </c>
       <c r="H14" t="n">
-        <v>1.951675737740761</v>
+        <v>1.915513755010844</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6039735809403104</v>
+        <v>0.603872972740517</v>
       </c>
       <c r="N14" t="n">
-        <v>1.042366852448362</v>
+        <v>1.042405720488156</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.013974493773963</v>
+        <v>3.988124868706906</v>
       </c>
       <c r="E15" t="n">
-        <v>215.647924632706</v>
+        <v>218.7216400905102</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06945073524001111</v>
+        <v>-0.0776327183435418</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7951052644175722</v>
+        <v>0.7953338508270813</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08734784983581378</v>
+        <v>-0.09761022778398053</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7173904858839248</v>
+        <v>0.7172325425141219</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137609829422649</v>
+        <v>1.137688836676435</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.933689011872034</v>
+        <v>3.925735730315933</v>
       </c>
       <c r="E16" t="n">
-        <v>179.2827818230267</v>
+        <v>179.8220118811337</v>
       </c>
       <c r="F16" t="n">
-        <v>0.428845028616444</v>
+        <v>0.4207406676678571</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9621529962315742</v>
+        <v>0.9622206098044356</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4457139667974678</v>
+        <v>0.4372600871159574</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158162376685548</v>
+        <v>0.5158014026617223</v>
       </c>
       <c r="N16" t="n">
-        <v>0.989810918760764</v>
+        <v>0.9898541696514513</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.335905840042511</v>
+        <v>3.327211345991469</v>
       </c>
       <c r="E17" t="n">
-        <v>59.39668048613846</v>
+        <v>59.28758502015374</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2246465331756468</v>
+        <v>-0.2264803915207152</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573409953431874</v>
+        <v>0.757345046978088</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.296625343876768</v>
+        <v>-0.2990451874273205</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244580757364104</v>
+        <v>0.7244563847029895</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094253182325021</v>
+        <v>1.094258873209952</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.114968255887765</v>
+        <v>3.097907509604551</v>
       </c>
       <c r="E18" t="n">
-        <v>53.84917280753641</v>
+        <v>54.33653912735844</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4712478422131086</v>
+        <v>-0.4745438151132929</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498568036179979</v>
+        <v>0.7498866621544983</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6284504453908749</v>
+        <v>-0.6328207168665753</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645591777183648</v>
+        <v>0.7645325364688973</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143411448800475</v>
+        <v>1.143419632725543</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.967560056128868</v>
+        <v>2.954944049584681</v>
       </c>
       <c r="E19" t="n">
-        <v>88.49913021767232</v>
+        <v>86.34590689820045</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1150053759251475</v>
+        <v>0.106545918210583</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837644919623301</v>
+        <v>0.483730460621527</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2377300894049552</v>
+        <v>0.2202588567064521</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7179208729771123</v>
+        <v>0.7179474071593145</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926656686236651</v>
+        <v>0.6926440541750735</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.573733701399156</v>
+        <v>2.562550922153811</v>
       </c>
       <c r="E20" t="n">
-        <v>103.6312354752308</v>
+        <v>103.2818238765441</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3295900895952948</v>
+        <v>-0.3336375321600182</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825496078982574</v>
+        <v>0.7825644361553842</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4211746913789856</v>
+        <v>-0.4263387355028895</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328424516699201</v>
+        <v>0.732827772770971</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143761809755295</v>
+        <v>1.143763071638908</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.8175165076744</v>
+        <v>568.5105650415796</v>
       </c>
       <c r="E2" t="n">
-        <v>10375.17266899911</v>
+        <v>10317.78963850989</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6250556471921012</v>
+        <v>0.6263242991018019</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014018786039043</v>
+        <v>0.5014024879530568</v>
       </c>
       <c r="H2" t="n">
-        <v>1.246616085548974</v>
+        <v>1.249144777200309</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.4570890773376</v>
+        <v>224.2142186653558</v>
       </c>
       <c r="E3" t="n">
-        <v>4178.257157636012</v>
+        <v>4168.724038618136</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2571843145211903</v>
+        <v>0.2616602012447191</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010689294179261</v>
+        <v>0.6010996151213198</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4278782381419167</v>
+        <v>0.4353025599457559</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907183993155562</v>
+        <v>0.8906898636226093</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067772534439166</v>
+        <v>1.067791538892676</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.88942399702586</v>
+        <v>37.15448376764509</v>
       </c>
       <c r="E4" t="n">
-        <v>1755.215496085001</v>
+        <v>1754.229703134217</v>
       </c>
       <c r="F4" t="n">
-        <v>0.761756513234386</v>
+        <v>0.786149583820082</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11468124215865</v>
+        <v>1.114710425495778</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6833850650964544</v>
+        <v>0.7052500504518334</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735662452418829</v>
+        <v>0.4735662276601524</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052799028117801</v>
+        <v>1.052825272747554</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.50852069960956</v>
+        <v>36.60335192732436</v>
       </c>
       <c r="E5" t="n">
-        <v>370.0828981346877</v>
+        <v>370.1825398547333</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3509851964588095</v>
+        <v>-0.3487417896949202</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5644736206188732</v>
+        <v>0.5644477803837999</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6217920264794644</v>
+        <v>-0.617845975862977</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366299651769679</v>
+        <v>0.7366557939579802</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292912357200724</v>
+        <v>0.8292813414307925</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.43455372362824</v>
+        <v>11.52601234314317</v>
       </c>
       <c r="E6" t="n">
-        <v>1459.3188580637</v>
+        <v>1493.324959114961</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4535906041620639</v>
+        <v>-0.4488208826234878</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8161976092269488</v>
+        <v>0.8173937673531343</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5557362568014337</v>
+        <v>-0.5490877231384445</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6704515359423083</v>
+        <v>0.6696733139233179</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091381911576242</v>
+        <v>1.091711361860828</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.58381478112146</v>
+        <v>10.62844917191066</v>
       </c>
       <c r="E7" t="n">
-        <v>180.3285084435689</v>
+        <v>178.4712611116411</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3315934229673613</v>
+        <v>-0.3258381031803163</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7183260325081172</v>
+        <v>0.71824033546852</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4616196656684779</v>
+        <v>-0.4536616604353844</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7510443878477887</v>
+        <v>0.7511266051073079</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075972704494747</v>
+        <v>1.075960805527779</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.369193047452695</v>
+        <v>9.423493010608057</v>
       </c>
       <c r="E8" t="n">
-        <v>357.0556344120241</v>
+        <v>355.0578672190242</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3711884911846909</v>
+        <v>-0.3652500825412712</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174336078469819</v>
+        <v>1.174296597586588</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3160836986873095</v>
+        <v>-0.3110373335764854</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395149216046094</v>
+        <v>0.7395385173404461</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732021937024131</v>
+        <v>1.732016863822227</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.306390086321613</v>
+        <v>7.324381877160748</v>
       </c>
       <c r="E9" t="n">
-        <v>213.2428486519044</v>
+        <v>214.3612691063081</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4141883091329075</v>
+        <v>0.4196469410089487</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824291586694995</v>
+        <v>0.4824321540192802</v>
       </c>
       <c r="H9" t="n">
-        <v>0.858547419221519</v>
+        <v>0.8698569063292113</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788683847885997</v>
+        <v>0.6788707881964844</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531804480525454</v>
+        <v>0.6531860222461827</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.574915325177023</v>
+        <v>6.606473361298441</v>
       </c>
       <c r="E10" t="n">
-        <v>232.2131401931072</v>
+        <v>237.3928040669489</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2876093571894656</v>
+        <v>-0.2809638913133982</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9636343059428863</v>
+        <v>0.9633603347055288</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.298463177800679</v>
+        <v>-0.2916498439800105</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7134047932798522</v>
+        <v>0.713566690149442</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371078494445843</v>
+        <v>1.37099807434829</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.536170353845875</v>
+        <v>6.558678673301257</v>
       </c>
       <c r="E11" t="n">
-        <v>364.8608492584005</v>
+        <v>362.0883603091747</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9291861174664535</v>
+        <v>0.9407572139266807</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8259124133153521</v>
+        <v>0.8258940584261085</v>
       </c>
       <c r="H11" t="n">
-        <v>1.125041956612013</v>
+        <v>1.139077348152213</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643018753135939</v>
+        <v>0.664316688288243</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094242340171982</v>
+        <v>1.094241091643599</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.227406653420942</v>
+        <v>6.245855211104109</v>
       </c>
       <c r="E12" t="n">
-        <v>93.11765205551686</v>
+        <v>93.13597319766887</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.290359508739045</v>
+        <v>-0.2860242833795209</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6620119555969249</v>
+        <v>0.6619342941381309</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4386016087537766</v>
+        <v>-0.4321037388641992</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7889758430886464</v>
+        <v>0.7890544888216772</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041702201547716</v>
+        <v>1.041682557713197</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.600462475400146</v>
+        <v>4.614678977169325</v>
       </c>
       <c r="E13" t="n">
-        <v>131.7268274266928</v>
+        <v>134.3289363260494</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3986730302047174</v>
+        <v>-0.3955782000122169</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8548936248812056</v>
+        <v>0.8549903516895512</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4663422659867376</v>
+        <v>-0.4626697824490213</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7602848878701731</v>
+        <v>0.7602316359999941</v>
       </c>
       <c r="N13" t="n">
-        <v>1.29629092245023</v>
+        <v>1.296345210576643</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.583397043740528</v>
+        <v>4.602965151572752</v>
       </c>
       <c r="E14" t="n">
-        <v>206.8139969343039</v>
+        <v>201.6269673318567</v>
       </c>
       <c r="F14" t="n">
-        <v>1.657915627499413</v>
+        <v>1.6888738806286</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8655200847096125</v>
+        <v>0.8653455325440599</v>
       </c>
       <c r="H14" t="n">
-        <v>1.915513755010844</v>
+        <v>1.951675737740761</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.603872972740517</v>
+        <v>0.6039806352440598</v>
       </c>
       <c r="N14" t="n">
-        <v>1.042405720488156</v>
+        <v>1.042380038011505</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.988124868706906</v>
+        <v>3.988672726644385</v>
       </c>
       <c r="E15" t="n">
-        <v>218.7216400905102</v>
+        <v>217.5320476041892</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0776327183435418</v>
+        <v>-0.07558904204110017</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7953338508270813</v>
+        <v>0.7952703467855848</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09761022778398053</v>
+        <v>-0.09504823403340092</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7172325425141219</v>
+        <v>0.7172452599213623</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137688836676435</v>
+        <v>1.137616785502234</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.925735730315933</v>
+        <v>3.91998402531892</v>
       </c>
       <c r="E16" t="n">
-        <v>179.8220118811337</v>
+        <v>179.1945114977826</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4207406676678571</v>
+        <v>0.4329018464452552</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9622206098044356</v>
+        <v>0.9621281119058986</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4372600871159574</v>
+        <v>0.4499419994991222</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158014026617223</v>
+        <v>0.5158401350745643</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9898541696514513</v>
+        <v>0.9898321351190427</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.327211345991469</v>
+        <v>3.339155264379611</v>
       </c>
       <c r="E17" t="n">
-        <v>59.28758502015374</v>
+        <v>58.70452997907044</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2264803915207152</v>
+        <v>-0.2213426524320112</v>
       </c>
       <c r="G17" t="n">
-        <v>0.757345046978088</v>
+        <v>0.7573471313857912</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2990451874273205</v>
+        <v>-0.2922605015047712</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244563847029895</v>
+        <v>0.7244608149135612</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094258873209952</v>
+        <v>1.09426724669058</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.097907509604551</v>
+        <v>3.107122643481086</v>
       </c>
       <c r="E18" t="n">
-        <v>54.33653912735844</v>
+        <v>54.62163153418623</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4745438151132929</v>
+        <v>-0.4722935057983413</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498866621544983</v>
+        <v>0.7498622354464082</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6328207168665753</v>
+        <v>-0.6298403673005021</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645325364688973</v>
+        <v>0.7645519663790096</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143419632725543</v>
+        <v>1.143410055591082</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.954944049584681</v>
+        <v>2.972394955794079</v>
       </c>
       <c r="E19" t="n">
-        <v>86.34590689820045</v>
+        <v>84.94726613040899</v>
       </c>
       <c r="F19" t="n">
-        <v>0.106545918210583</v>
+        <v>0.1197125398039971</v>
       </c>
       <c r="G19" t="n">
-        <v>0.483730460621527</v>
+        <v>0.4838209810011482</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2202588567064521</v>
+        <v>0.2474314767339802</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7179474071593145</v>
+        <v>0.7178432264856178</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926440541750735</v>
+        <v>0.6926722989771393</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.562550922153811</v>
+        <v>2.570795752186132</v>
       </c>
       <c r="E20" t="n">
-        <v>103.2818238765441</v>
+        <v>102.4373131563563</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3336375321600182</v>
+        <v>-0.3295900895952948</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825644361553842</v>
+        <v>0.7825496078982574</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4263387355028895</v>
+        <v>-0.4211746913789856</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732827772770971</v>
+        <v>0.7328429571922355</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143763071638908</v>
+        <v>1.14376370796045</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.5105650415796</v>
+        <v>567.94267994566</v>
       </c>
       <c r="E2" t="n">
-        <v>10317.78963850989</v>
+        <v>10273.15251002728</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6263242991018019</v>
+        <v>0.6244483998427319</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014024879530568</v>
+        <v>0.5014018983491068</v>
       </c>
       <c r="H2" t="n">
-        <v>1.249144777200309</v>
+        <v>1.245404937433948</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.2142186653558</v>
+        <v>223.7989437858506</v>
       </c>
       <c r="E3" t="n">
-        <v>4168.724038618136</v>
+        <v>4168.665939833965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2616602012447191</v>
+        <v>0.2590240897562202</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6010996151213198</v>
+        <v>0.601079687662623</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4353025599457559</v>
+        <v>0.43093136413155</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906898636226093</v>
+        <v>0.8906968305476138</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067791538892676</v>
+        <v>1.067765747338442</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.15448376764509</v>
+        <v>37.40732323543589</v>
       </c>
       <c r="E4" t="n">
-        <v>1754.229703134217</v>
+        <v>1783.276049603879</v>
       </c>
       <c r="F4" t="n">
-        <v>0.786149583820082</v>
+        <v>0.7889037369487661</v>
       </c>
       <c r="G4" t="n">
-        <v>1.114710425495778</v>
+        <v>1.114721467527769</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7052500504518334</v>
+        <v>0.7077137741846834</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735662276601524</v>
+        <v>0.47354645738248</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052825272747554</v>
+        <v>1.052792986332965</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.60335192732436</v>
+        <v>36.58608222126859</v>
       </c>
       <c r="E5" t="n">
-        <v>370.1825398547333</v>
+        <v>366.6301461509241</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3487417896949202</v>
+        <v>-0.3498637528863531</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5644477803837999</v>
+        <v>0.5644588172669761</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.617845975862977</v>
+        <v>-0.6198215745487691</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366557939579802</v>
+        <v>0.7366555329826784</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292813414307925</v>
+        <v>0.8292982380993357</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.52601234314317</v>
+        <v>11.47952736627925</v>
       </c>
       <c r="E6" t="n">
-        <v>1493.324959114961</v>
+        <v>1502.708082110986</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4488208826234878</v>
+        <v>-0.451207134695181</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8173937673531343</v>
+        <v>0.81678577305922</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5490877231384445</v>
+        <v>-0.5524179651234778</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6696733139233179</v>
+        <v>0.6698767678772377</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091711361860828</v>
+        <v>1.09123203463435</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.62844917191066</v>
+        <v>10.63994908056643</v>
       </c>
       <c r="E7" t="n">
-        <v>178.4712611116411</v>
+        <v>177.7116074833049</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3258381031803163</v>
+        <v>-0.3249281584458512</v>
       </c>
       <c r="G7" t="n">
-        <v>0.71824033546852</v>
+        <v>0.7182334498449124</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4536616604353844</v>
+        <v>-0.4523990890650006</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511266051073079</v>
+        <v>0.7511474645824288</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075960805527779</v>
+        <v>1.075981635900517</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.423493010608057</v>
+        <v>9.394395454865935</v>
       </c>
       <c r="E8" t="n">
-        <v>355.0578672190242</v>
+        <v>341.0841255759833</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3652500825412712</v>
+        <v>-0.3700761816552717</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174296597586588</v>
+        <v>1.174324576512671</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3110373335764854</v>
+        <v>-0.3151396036982103</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395385173404461</v>
+        <v>0.7395269505838047</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732016863822227</v>
+        <v>1.732033077504163</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.324381877160748</v>
+        <v>7.321712945274749</v>
       </c>
       <c r="E9" t="n">
-        <v>214.3612691063081</v>
+        <v>213.8587961787006</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4196469410089487</v>
+        <v>0.4165609335449771</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824321540192802</v>
+        <v>0.4824277246640369</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8698569063292113</v>
+        <v>0.8634680642267617</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788707881964844</v>
+        <v>0.6788708307086828</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531860222461827</v>
+        <v>0.6531808341330703</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.606473361298441</v>
+        <v>6.605775141997009</v>
       </c>
       <c r="E10" t="n">
-        <v>237.3928040669489</v>
+        <v>237.5584417126089</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2809638913133982</v>
+        <v>-0.281241116275077</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9633603347055288</v>
+        <v>0.9633705369631869</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2916498439800105</v>
+        <v>-0.2919345210220229</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713566690149442</v>
+        <v>0.713622423708565</v>
       </c>
       <c r="N10" t="n">
-        <v>1.37099807434829</v>
+        <v>1.371121289689301</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.558678673301257</v>
+        <v>6.583117633943488</v>
       </c>
       <c r="E11" t="n">
-        <v>362.0883603091747</v>
+        <v>367.6447069773695</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9407572139266807</v>
+        <v>0.9481843448634506</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258940584261085</v>
+        <v>0.8258987289138447</v>
       </c>
       <c r="H11" t="n">
-        <v>1.139077348152213</v>
+        <v>1.148063693124248</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.664316688288243</v>
+        <v>0.6643132702375876</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094241091643599</v>
+        <v>1.09424293624795</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.245855211104109</v>
+        <v>6.363808099993728</v>
       </c>
       <c r="E12" t="n">
-        <v>93.13597319766887</v>
+        <v>93.23071083390637</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2860242833795209</v>
+        <v>-0.2865901494488148</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6619342941381309</v>
+        <v>0.6619421723346195</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4321037388641992</v>
+        <v>-0.4329534533780092</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890544888216772</v>
+        <v>0.7890684963870195</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041682557713197</v>
+        <v>1.041714673077616</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.614678977169325</v>
+        <v>4.622710659141288</v>
       </c>
       <c r="E13" t="n">
-        <v>134.3289363260494</v>
+        <v>136.3579814436565</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3955782000122169</v>
+        <v>-0.394339074416225</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8549903516895512</v>
+        <v>0.8550354618088962</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4626697824490213</v>
+        <v>-0.4611961632351119</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7602316359999941</v>
+        <v>0.7601437811154726</v>
       </c>
       <c r="N13" t="n">
-        <v>1.296345210576643</v>
+        <v>1.296265313448602</v>
       </c>
     </row>
     <row r="14">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.602965151572752</v>
+        <v>4.610674665553484</v>
       </c>
       <c r="E14" t="n">
-        <v>201.6269673318567</v>
+        <v>201.3464079649613</v>
       </c>
       <c r="F14" t="n">
         <v>1.6888738806286</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6039806352440598</v>
+        <v>0.604005424570803</v>
       </c>
       <c r="N14" t="n">
-        <v>1.042380038011505</v>
+        <v>1.042424046469814</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.988672726644385</v>
+        <v>3.985700953754455</v>
       </c>
       <c r="E15" t="n">
-        <v>217.5320476041892</v>
+        <v>213.3167068281537</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07558904204110017</v>
+        <v>-0.07712191313054872</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7952703467855848</v>
+        <v>0.7953175775892852</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09504823403340092</v>
+        <v>-0.09696995930143483</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7172452599213623</v>
+        <v>0.7172696288244034</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137616785502234</v>
+        <v>1.137724339603124</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.91998402531892</v>
+        <v>3.962280625441995</v>
       </c>
       <c r="E16" t="n">
-        <v>179.1945114977826</v>
+        <v>185.0607093686083</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4329018464452552</v>
+        <v>0.4478032182792062</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9621281119058986</v>
+        <v>0.9620877683521549</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4499419994991222</v>
+        <v>0.4654494454764712</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158401350745643</v>
+        <v>0.5158768551120655</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9898321351190427</v>
+        <v>0.9898622520446209</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.339155264379611</v>
+        <v>3.339970319749193</v>
       </c>
       <c r="E17" t="n">
-        <v>58.70452997907044</v>
+        <v>58.35962871147267</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2213426524320112</v>
+        <v>-0.2222607753804239</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573471313857912</v>
+        <v>0.7573436950241286</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2922605015047712</v>
+        <v>-0.2934741212486661</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244608149135612</v>
+        <v>0.7244574561429242</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09426724669058</v>
+        <v>1.094258495090599</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.107122643481086</v>
+        <v>3.105478434087735</v>
       </c>
       <c r="E18" t="n">
-        <v>54.62163153418623</v>
+        <v>54.91555949542242</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4722935057983413</v>
+        <v>-0.4733386133590767</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498622354464082</v>
+        <v>0.7498714145901196</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6298403673005021</v>
+        <v>-0.6312263731479936</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645519663790096</v>
+        <v>0.7645528913543963</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143410055591082</v>
+        <v>1.143426780107061</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.972394955794079</v>
+        <v>2.979609555158373</v>
       </c>
       <c r="E19" t="n">
-        <v>84.94726613040899</v>
+        <v>84.55690094770847</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1197125398039971</v>
+        <v>0.1225393919526083</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4838209810011482</v>
+        <v>0.4838677555492443</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2474314767339802</v>
+        <v>0.2532497579085681</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7178432264856178</v>
+        <v>0.7177349876066346</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926722989771393</v>
+        <v>0.6926356255846946</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.570795752186132</v>
+        <v>2.569056503132301</v>
       </c>
       <c r="E20" t="n">
-        <v>102.4373131563563</v>
+        <v>100.7067013226537</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3295900895952948</v>
+        <v>-0.3311086516355367</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825496078982574</v>
+        <v>0.7825512241227631</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4211746913789856</v>
+        <v>-0.4231143488488031</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328429571922355</v>
+        <v>0.7328424741449635</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14376370796045</v>
+        <v>1.143766661274183</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-25.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.94267994566</v>
+        <v>567.7669859021971</v>
       </c>
       <c r="E2" t="n">
-        <v>10273.15251002728</v>
+        <v>10253.161421113</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6244483998427319</v>
+        <v>0.6237606651242995</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5014018983491068</v>
+        <v>0.5014021642855789</v>
       </c>
       <c r="H2" t="n">
-        <v>1.245404937433948</v>
+        <v>1.244032653933719</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.7989437858506</v>
+        <v>223.3938892529282</v>
       </c>
       <c r="E3" t="n">
-        <v>4168.665939833965</v>
+        <v>4149.706979961487</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2590240897562202</v>
+        <v>0.2549756903188742</v>
       </c>
       <c r="G3" t="n">
-        <v>0.601079687662623</v>
+        <v>0.6010594390853808</v>
       </c>
       <c r="H3" t="n">
-        <v>0.43093136413155</v>
+        <v>0.4242104419936658</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906968305476138</v>
+        <v>0.8907244502805242</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067765747338442</v>
+        <v>1.067762320547774</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.40732323543589</v>
+        <v>37.47195373216569</v>
       </c>
       <c r="E4" t="n">
-        <v>1783.276049603879</v>
+        <v>1810.91237393092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7889037369487661</v>
+        <v>0.7933816645746612</v>
       </c>
       <c r="G4" t="n">
-        <v>1.114721467527769</v>
+        <v>1.114742759880181</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7077137741846834</v>
+        <v>0.7117172617115169</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.47354645738248</v>
+        <v>0.4735286232464935</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052792986332965</v>
+        <v>1.052772887632389</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.58608222126859</v>
+        <v>36.57548095773513</v>
       </c>
       <c r="E5" t="n">
-        <v>366.6301461509241</v>
+        <v>366.0402933463341</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3498637528863531</v>
+        <v>-0.3502376251664492</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5644588172669761</v>
+        <v>0.5644633332341663</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6198215745487691</v>
+        <v>-0.6204789656747357</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366555329826784</v>
+        <v>0.7366565586009834</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292982380993357</v>
+        <v>0.829305587679691</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.47952736627925</v>
+        <v>11.3996741177265</v>
       </c>
       <c r="E6" t="n">
-        <v>1502.708082110986</v>
+        <v>1515.012616626593</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.451207134695181</v>
+        <v>-0.4545065810703646</v>
       </c>
       <c r="G6" t="n">
-        <v>0.81678577305922</v>
+        <v>0.8159766817919624</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5524179651234778</v>
+        <v>-0.5570092763830271</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6698767678772377</v>
+        <v>0.6704425190886322</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09123203463435</v>
+        <v>1.091071201971516</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.63994908056643</v>
+        <v>10.63910341240774</v>
       </c>
       <c r="E7" t="n">
-        <v>177.7116074833049</v>
+        <v>178.6493035688557</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3249281584458512</v>
+        <v>-0.3261413448483301</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7182334498449124</v>
+        <v>0.7182430334680865</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4523990890650006</v>
+        <v>-0.4540821555533006</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511474645824288</v>
+        <v>0.751143132516996</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075981635900517</v>
+        <v>1.075989216832435</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.394395454865935</v>
+        <v>9.372183396681372</v>
       </c>
       <c r="E8" t="n">
-        <v>341.0841255759833</v>
+        <v>340.1915478286172</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3700761816552717</v>
+        <v>-0.3711884911846909</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174324576512671</v>
+        <v>1.174336078469819</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3151396036982103</v>
+        <v>-0.3160836986873095</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395269505838047</v>
+        <v>0.7395257951958956</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732033077504163</v>
+        <v>1.732046417260749</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.321712945274749</v>
+        <v>7.340963946230034</v>
       </c>
       <c r="E9" t="n">
-        <v>213.8587961787006</v>
+        <v>214.686443036302</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4165609335449771</v>
+        <v>0.4234475778623576</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4824277246640369</v>
+        <v>0.4824473718129908</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8634680642267617</v>
+        <v>0.8777072953492987</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788708307086828</v>
+        <v>0.6788330845335434</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531808341330703</v>
+        <v>0.6531707696147518</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.605775141997009</v>
+        <v>6.592439172812103</v>
       </c>
       <c r="E10" t="n">
-        <v>237.5584417126089</v>
+        <v>239.438622405142</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.281241116275077</v>
+        <v>-0.2838733209839712</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9633705369631869</v>
+        <v>0.9634727208697134</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2919345210220229</v>
+        <v>-0.2946355561865029</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713622423708565</v>
+        <v>0.7135729019622697</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371121289689301</v>
+        <v>1.371170837230187</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.583117633943488</v>
+        <v>6.570931611213312</v>
       </c>
       <c r="E11" t="n">
-        <v>367.6447069773695</v>
+        <v>367.279075134499</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9481843448634506</v>
+        <v>0.941945042922909</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258987289138447</v>
+        <v>0.8258939427854689</v>
       </c>
       <c r="H11" t="n">
-        <v>1.148063693124248</v>
+        <v>1.14051574194386</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643132702375876</v>
+        <v>0.6643179564382382</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09424293624795</v>
+        <v>1.09424373364585</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.363808099993728</v>
+        <v>6.359156848503226</v>
       </c>
       <c r="E12" t="n">
-        <v>93.23071083390637</v>
+        <v>94.37414944469714</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2865901494488148</v>
+        <v>-0.2875329918004785</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6619421723346195</v>
+        <v>0.6619568038086296</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4329534533780092</v>
+        <v>-0.4343682097474199</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,45 +1084,45 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890684963870195</v>
+        <v>0.7890613097135047</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041714673077616</v>
+        <v>1.041727658537803</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.622710659141288</v>
+        <v>4.615239184613058</v>
       </c>
       <c r="E13" t="n">
-        <v>136.3579814436565</v>
+        <v>200.3604973447746</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.394339074416225</v>
+        <v>1.693525911024945</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8550354618088962</v>
+        <v>0.8653288051121129</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4611961632351119</v>
+        <v>1.957089491324087</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4691011235955056</v>
+        <v>0.3000688231245698</v>
       </c>
       <c r="J13" t="n">
         <v>267</v>
@@ -1138,45 +1138,45 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7601437811154726</v>
+        <v>0.6040237566009902</v>
       </c>
       <c r="N13" t="n">
-        <v>1.296265313448602</v>
+        <v>1.042434980917168</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.610674665553484</v>
+        <v>4.613791529623692</v>
       </c>
       <c r="E14" t="n">
-        <v>201.3464079649613</v>
+        <v>136.6367585174929</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6888738806286</v>
+        <v>-0.3961975072180657</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8653455325440599</v>
+        <v>0.854969172081383</v>
       </c>
       <c r="H14" t="n">
-        <v>1.951675737740761</v>
+        <v>-0.4634056059045277</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3000688231245698</v>
+        <v>0.4691011235955056</v>
       </c>
       <c r="J14" t="n">
         <v>267</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.604005424570803</v>
+        <v>0.7601866886416444</v>
       </c>
       <c r="N14" t="n">
-        <v>1.042424046469814</v>
+        <v>1.296237292356514</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.985700953754455</v>
+        <v>3.990463562735333</v>
       </c>
       <c r="E15" t="n">
-        <v>213.3167068281537</v>
+        <v>211.0149899890984</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07712191313054872</v>
+        <v>-0.07661103199617847</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7953175775892852</v>
+        <v>0.7953015691591537</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09696995930143483</v>
+        <v>-0.09632953708010007</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7172696288244034</v>
+        <v>0.7173083020892526</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137724339603124</v>
+        <v>1.137762177463498</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.962280625441995</v>
+        <v>3.978727297217713</v>
       </c>
       <c r="E16" t="n">
-        <v>185.0607093686083</v>
+        <v>189.3840413984588</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4478032182792062</v>
+        <v>0.4505170008872577</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9620877683521549</v>
+        <v>0.9620890270415504</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4654494454764712</v>
+        <v>0.4682695553369001</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158768551120655</v>
+        <v>0.5158741156225953</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9898622520446209</v>
+        <v>0.9898577655372474</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.339970319749193</v>
+        <v>3.341675962512055</v>
       </c>
       <c r="E17" t="n">
-        <v>58.35962871147267</v>
+        <v>57.12069165522508</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2222607753804239</v>
+        <v>-0.2231786074157042</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573436950241286</v>
+        <v>0.757341590892017</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2934741212486661</v>
+        <v>-0.2946868495005516</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244574561429242</v>
+        <v>0.7244585592259296</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094258495090599</v>
+        <v>1.094256540677809</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.105478434087735</v>
+        <v>3.105793999071199</v>
       </c>
       <c r="E18" t="n">
-        <v>54.91555949542242</v>
+        <v>55.72890532464724</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4733386133590767</v>
+        <v>-0.4736600729743222</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7498714145901196</v>
+        <v>0.7498749928199921</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6312263731479936</v>
+        <v>-0.6316520453536775</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645528913543963</v>
+        <v>0.7645543287811769</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143426780107061</v>
+        <v>1.143433779593217</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.979609555158373</v>
+        <v>2.97557457981479</v>
       </c>
       <c r="E19" t="n">
-        <v>84.55690094770847</v>
+        <v>83.11606017987059</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1225393919526083</v>
+        <v>0.1197125398039971</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4838677555492443</v>
+        <v>0.4838209810011482</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2532497579085681</v>
+        <v>0.2474314767339802</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177349876066346</v>
+        <v>0.7177917561632102</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926356255846946</v>
+        <v>0.6926230805490159</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.569056503132301</v>
+        <v>2.567999568370683</v>
       </c>
       <c r="E20" t="n">
-        <v>100.7067013226537</v>
+        <v>100.4390483726841</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3311086516355367</v>
+        <v>-0.331614633457435</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7825512241227631</v>
+        <v>0.7825528147060347</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4231143488488031</v>
+        <v>-0.423760067340638</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328424741449635</v>
+        <v>0.7328429822110182</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143766661274183</v>
+        <v>1.143769172364721</v>
       </c>
     </row>
   </sheetData>
